--- a/data_files/2026-06/ventas/ventas 29-30.xlsx
+++ b/data_files/2026-06/ventas/ventas 29-30.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1733" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1805" uniqueCount="96">
   <si>
     <t>Periodos</t>
   </si>
@@ -1114,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK213"/>
+  <dimension ref="A1:AK222"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.42578125" bestFit="1" customWidth="1"/>
@@ -1384,16 +1384,16 @@
         <v>337500</v>
       </c>
       <c r="AE3">
-        <v>4.76</v>
+        <v>4.8</v>
       </c>
       <c r="AF3">
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1606500</v>
+        <v>1620000</v>
       </c>
       <c r="AH3">
-        <v>1606500</v>
+        <v>1620000</v>
       </c>
       <c r="AI3">
         <v>14</v>
@@ -1656,22 +1656,22 @@
         <v>402500</v>
       </c>
       <c r="AE7">
-        <v>0.24</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF7">
         <v>0</v>
       </c>
       <c r="AG7">
-        <v>96600</v>
+        <v>112700</v>
       </c>
       <c r="AH7">
-        <v>96600</v>
+        <v>112700</v>
       </c>
       <c r="AI7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ7">
-        <v>0.08</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -2336,22 +2336,22 @@
         <v>205000</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="AF17">
         <v>0</v>
       </c>
       <c r="AG17">
-        <v>213200</v>
+        <v>418200</v>
       </c>
       <c r="AH17">
-        <v>213200</v>
+        <v>418200</v>
       </c>
       <c r="AI17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ17">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="AK17">
         <v>0</v>
@@ -2404,22 +2404,22 @@
         <v>337500</v>
       </c>
       <c r="AE18">
-        <v>2.72</v>
+        <v>3.12</v>
       </c>
       <c r="AF18">
         <v>0</v>
       </c>
       <c r="AG18">
-        <v>918000</v>
+        <v>1053000</v>
       </c>
       <c r="AH18">
-        <v>918000</v>
+        <v>1053000</v>
       </c>
       <c r="AI18">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ18">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AK18">
         <v>0</v>
@@ -2472,16 +2472,16 @@
         <v>337500</v>
       </c>
       <c r="AE19">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="AF19">
         <v>0</v>
       </c>
       <c r="AG19">
-        <v>67500</v>
+        <v>108000</v>
       </c>
       <c r="AH19">
-        <v>67500</v>
+        <v>108000</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -2540,19 +2540,19 @@
         <v>337500</v>
       </c>
       <c r="AE20">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="AF20">
         <v>0</v>
       </c>
       <c r="AG20">
-        <v>148500</v>
+        <v>202500</v>
       </c>
       <c r="AH20">
-        <v>148500</v>
+        <v>202500</v>
       </c>
       <c r="AI20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AJ20">
         <v>7.0000000000000007E-2</v>
@@ -2608,22 +2608,22 @@
         <v>402500</v>
       </c>
       <c r="AE21">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="AF21">
         <v>0</v>
       </c>
       <c r="AG21">
-        <v>64400</v>
+        <v>80500</v>
       </c>
       <c r="AH21">
-        <v>64400</v>
+        <v>80500</v>
       </c>
       <c r="AI21">
         <v>2</v>
       </c>
       <c r="AJ21">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AK21">
         <v>0</v>
@@ -2676,22 +2676,22 @@
         <v>337500</v>
       </c>
       <c r="AE22">
-        <v>2.64</v>
+        <v>2.96</v>
       </c>
       <c r="AF22">
         <v>0</v>
       </c>
       <c r="AG22">
-        <v>891000</v>
+        <v>999000</v>
       </c>
       <c r="AH22">
-        <v>891000</v>
+        <v>999000</v>
       </c>
       <c r="AI22">
         <v>6</v>
       </c>
       <c r="AJ22">
-        <v>0.44</v>
+        <v>0.49</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -3220,22 +3220,22 @@
         <v>337500</v>
       </c>
       <c r="AE30">
-        <v>5.96</v>
+        <v>6.16</v>
       </c>
       <c r="AF30">
         <v>0</v>
       </c>
       <c r="AG30">
-        <v>2011500</v>
+        <v>2079000</v>
       </c>
       <c r="AH30">
-        <v>2011500</v>
+        <v>2079000</v>
       </c>
       <c r="AI30">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ30">
-        <v>0.66</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AK30">
         <v>0</v>
@@ -3424,22 +3424,22 @@
         <v>402500</v>
       </c>
       <c r="AE33">
-        <v>3.72</v>
+        <v>3.76</v>
       </c>
       <c r="AF33">
         <v>0</v>
       </c>
       <c r="AG33">
-        <v>1497300</v>
+        <v>1513400</v>
       </c>
       <c r="AH33">
-        <v>1497300</v>
+        <v>1513400</v>
       </c>
       <c r="AI33">
         <v>7</v>
       </c>
       <c r="AJ33">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AK33">
         <v>0</v>
@@ -3560,22 +3560,22 @@
         <v>337500</v>
       </c>
       <c r="AE35">
-        <v>6.2</v>
+        <v>7.68</v>
       </c>
       <c r="AF35">
         <v>0</v>
       </c>
       <c r="AG35">
-        <v>2092500</v>
+        <v>2592000</v>
       </c>
       <c r="AH35">
-        <v>2092500</v>
+        <v>2592000</v>
       </c>
       <c r="AI35">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ35">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="AK35">
         <v>0</v>
@@ -3900,22 +3900,22 @@
         <v>205000</v>
       </c>
       <c r="AE40">
-        <v>0.92</v>
+        <v>1.36</v>
       </c>
       <c r="AF40">
         <v>0</v>
       </c>
       <c r="AG40">
-        <v>188600</v>
+        <v>278800</v>
       </c>
       <c r="AH40">
-        <v>188600</v>
+        <v>278800</v>
       </c>
       <c r="AI40">
         <v>11</v>
       </c>
       <c r="AJ40">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="AK40">
         <v>0</v>
@@ -4852,22 +4852,22 @@
         <v>337500</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.44</v>
       </c>
       <c r="AF54">
         <v>0</v>
       </c>
       <c r="AG54">
-        <v>364500</v>
+        <v>486000</v>
       </c>
       <c r="AH54">
-        <v>364500</v>
+        <v>486000</v>
       </c>
       <c r="AI54">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ54">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="AK54">
         <v>0</v>
@@ -4920,22 +4920,22 @@
         <v>402500</v>
       </c>
       <c r="AE55">
-        <v>0.84</v>
+        <v>1.28</v>
       </c>
       <c r="AF55">
         <v>0</v>
       </c>
       <c r="AG55">
-        <v>338100</v>
+        <v>515200</v>
       </c>
       <c r="AH55">
-        <v>338100</v>
+        <v>515200</v>
       </c>
       <c r="AI55">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ55">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="AK55">
         <v>0</v>
@@ -4988,22 +4988,22 @@
         <v>337500</v>
       </c>
       <c r="AE56">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AF56">
         <v>0</v>
       </c>
       <c r="AG56">
-        <v>1620000</v>
+        <v>2092500</v>
       </c>
       <c r="AH56">
-        <v>1620000</v>
+        <v>2092500</v>
       </c>
       <c r="AI56">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ56">
-        <v>0.53</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AK56">
         <v>0</v>
@@ -5056,22 +5056,22 @@
         <v>337500</v>
       </c>
       <c r="AE57">
-        <v>0.48</v>
+        <v>0.52</v>
       </c>
       <c r="AF57">
         <v>0</v>
       </c>
       <c r="AG57">
-        <v>162000</v>
+        <v>175500</v>
       </c>
       <c r="AH57">
-        <v>162000</v>
+        <v>175500</v>
       </c>
       <c r="AI57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="AK57">
         <v>0</v>
@@ -5328,19 +5328,19 @@
         <v>205000</v>
       </c>
       <c r="AE61">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="AF61">
         <v>0</v>
       </c>
       <c r="AG61">
-        <v>533000</v>
+        <v>606800</v>
       </c>
       <c r="AH61">
-        <v>533000</v>
+        <v>606800</v>
       </c>
       <c r="AI61">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ61">
         <v>0.19</v>
@@ -5396,22 +5396,22 @@
         <v>337500</v>
       </c>
       <c r="AE62">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF62">
         <v>0</v>
       </c>
       <c r="AG62">
-        <v>351000</v>
+        <v>364500</v>
       </c>
       <c r="AH62">
-        <v>351000</v>
+        <v>364500</v>
       </c>
       <c r="AI62">
         <v>3</v>
       </c>
       <c r="AJ62">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="AK62">
         <v>0</v>
@@ -5668,22 +5668,22 @@
         <v>402500</v>
       </c>
       <c r="AE66">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="AF66">
         <v>0</v>
       </c>
       <c r="AG66">
-        <v>740600</v>
+        <v>772800</v>
       </c>
       <c r="AH66">
-        <v>740600</v>
+        <v>772800</v>
       </c>
       <c r="AI66">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ66">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
       <c r="AK66">
         <v>0</v>
@@ -5736,22 +5736,22 @@
         <v>337500</v>
       </c>
       <c r="AE67">
-        <v>7.56</v>
+        <v>7.64</v>
       </c>
       <c r="AF67">
         <v>0</v>
       </c>
       <c r="AG67">
-        <v>2551500</v>
+        <v>2578500</v>
       </c>
       <c r="AH67">
-        <v>2551500</v>
+        <v>2578500</v>
       </c>
       <c r="AI67">
         <v>12</v>
       </c>
       <c r="AJ67">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="AK67">
         <v>0</v>
@@ -6271,31 +6271,31 @@
         <v>31</v>
       </c>
       <c r="AB75">
-        <v>337500</v>
+        <v>322500</v>
       </c>
       <c r="AC75" s="1">
         <v>0</v>
       </c>
       <c r="AD75">
-        <v>337500</v>
+        <v>322500</v>
       </c>
       <c r="AE75">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AF75">
         <v>0</v>
       </c>
       <c r="AG75">
-        <v>1755000</v>
+        <v>1612500</v>
       </c>
       <c r="AH75">
-        <v>1755000</v>
+        <v>1612500</v>
       </c>
       <c r="AI75">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="AJ75">
-        <v>0.25</v>
+        <v>1.67</v>
       </c>
       <c r="AK75">
         <v>0</v>
@@ -6321,13 +6321,13 @@
         <v>71</v>
       </c>
       <c r="G76" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H76">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="I76" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J76">
         <v>1005</v>
@@ -6348,22 +6348,22 @@
         <v>337500</v>
       </c>
       <c r="AE76">
-        <v>0.64</v>
+        <v>5.42</v>
       </c>
       <c r="AF76">
         <v>0</v>
       </c>
       <c r="AG76">
-        <v>216000</v>
+        <v>1829250</v>
       </c>
       <c r="AH76">
-        <v>216000</v>
+        <v>1829250</v>
       </c>
       <c r="AI76">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AJ76">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="AK76">
         <v>0</v>
@@ -6389,13 +6389,13 @@
         <v>71</v>
       </c>
       <c r="G77" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H77">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="I77" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J77">
         <v>1005</v>
@@ -6416,22 +6416,22 @@
         <v>337500</v>
       </c>
       <c r="AE77">
-        <v>0.28000000000000003</v>
+        <v>0.64</v>
       </c>
       <c r="AF77">
         <v>0</v>
       </c>
       <c r="AG77">
-        <v>94500</v>
+        <v>216000</v>
       </c>
       <c r="AH77">
-        <v>94500</v>
+        <v>216000</v>
       </c>
       <c r="AI77">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AJ77">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="AK77">
         <v>0</v>
@@ -6457,13 +6457,13 @@
         <v>71</v>
       </c>
       <c r="G78" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H78">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="I78" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J78">
         <v>1005</v>
@@ -6475,31 +6475,31 @@
         <v>31</v>
       </c>
       <c r="AB78">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC78" s="1">
         <v>0</v>
       </c>
       <c r="AD78">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE78">
-        <v>1.6</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF78">
         <v>0</v>
       </c>
       <c r="AG78">
-        <v>644000</v>
+        <v>94500</v>
       </c>
       <c r="AH78">
-        <v>644000</v>
+        <v>94500</v>
       </c>
       <c r="AI78">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AJ78">
-        <v>0.11</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK78">
         <v>0</v>
@@ -6525,49 +6525,49 @@
         <v>71</v>
       </c>
       <c r="G79" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H79">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="I79" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J79">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K79" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L79" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB79">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AC79" s="1">
         <v>0</v>
       </c>
       <c r="AD79">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AE79">
-        <v>5.64</v>
+        <v>1.708</v>
       </c>
       <c r="AF79">
         <v>0</v>
       </c>
       <c r="AG79">
-        <v>1903500</v>
+        <v>687470</v>
       </c>
       <c r="AH79">
-        <v>1903500</v>
+        <v>687470</v>
       </c>
       <c r="AI79">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AJ79">
-        <v>0.81</v>
+        <v>0.11</v>
       </c>
       <c r="AK79">
         <v>0</v>
@@ -6593,22 +6593,22 @@
         <v>71</v>
       </c>
       <c r="G80" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H80">
-        <v>10007</v>
+        <v>10005</v>
       </c>
       <c r="I80" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J80">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K80" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L80" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AB80">
         <v>337500</v>
@@ -6620,22 +6620,22 @@
         <v>337500</v>
       </c>
       <c r="AE80">
-        <v>0.65200000000000002</v>
+        <v>5.64</v>
       </c>
       <c r="AF80">
         <v>0</v>
       </c>
       <c r="AG80">
-        <v>220050</v>
+        <v>1903500</v>
       </c>
       <c r="AH80">
-        <v>220050</v>
+        <v>1903500</v>
       </c>
       <c r="AI80">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ80">
-        <v>0.08</v>
+        <v>0.81</v>
       </c>
       <c r="AK80">
         <v>0</v>
@@ -6661,49 +6661,49 @@
         <v>71</v>
       </c>
       <c r="G81" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H81">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="I81" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J81">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L81" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AB81">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AC81" s="1">
         <v>0</v>
       </c>
       <c r="AD81">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AE81">
-        <v>0.04</v>
+        <v>0.65200000000000002</v>
       </c>
       <c r="AF81">
         <v>0</v>
       </c>
       <c r="AG81">
-        <v>9500</v>
+        <v>220050</v>
       </c>
       <c r="AH81">
-        <v>9500</v>
+        <v>220050</v>
       </c>
       <c r="AI81">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK81">
         <v>0</v>
@@ -6729,43 +6729,43 @@
         <v>71</v>
       </c>
       <c r="G82" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H82">
-        <v>10010</v>
+        <v>10008</v>
       </c>
       <c r="I82" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="J82">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K82" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L82" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB82">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AC82" s="1">
         <v>0</v>
       </c>
       <c r="AD82">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AE82">
-        <v>0.16</v>
+        <v>0.04</v>
       </c>
       <c r="AF82">
         <v>0</v>
       </c>
       <c r="AG82">
-        <v>64400</v>
+        <v>9500</v>
       </c>
       <c r="AH82">
-        <v>64400</v>
+        <v>9500</v>
       </c>
       <c r="AI82">
         <v>0</v>
@@ -6797,49 +6797,49 @@
         <v>71</v>
       </c>
       <c r="G83" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H83">
-        <v>11005</v>
+        <v>10010</v>
       </c>
       <c r="I83" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J83">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="K83" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L83" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB83">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AC83" s="1">
         <v>0</v>
       </c>
       <c r="AD83">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AE83">
-        <v>1.04</v>
+        <v>0.16</v>
       </c>
       <c r="AF83">
         <v>0</v>
       </c>
       <c r="AG83">
-        <v>213200</v>
+        <v>64400</v>
       </c>
       <c r="AH83">
-        <v>213200</v>
+        <v>64400</v>
       </c>
       <c r="AI83">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AJ83">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="AK83">
         <v>0</v>
@@ -6856,58 +6856,58 @@
         <v>25</v>
       </c>
       <c r="D84" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E84">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F84" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G84" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H84">
-        <v>10001</v>
+        <v>11005</v>
       </c>
       <c r="I84" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J84">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K84" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L84" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB84">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AC84" s="1">
         <v>0</v>
       </c>
       <c r="AD84">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AE84">
-        <v>0.48</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="AF84">
         <v>0</v>
       </c>
       <c r="AG84">
-        <v>158400</v>
+        <v>233700</v>
       </c>
       <c r="AH84">
-        <v>158400</v>
+        <v>233700</v>
       </c>
       <c r="AI84">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK84">
         <v>0</v>
@@ -6951,31 +6951,31 @@
         <v>31</v>
       </c>
       <c r="AB85">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC85" s="1">
         <v>0</v>
       </c>
       <c r="AD85">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE85">
-        <v>2.12</v>
+        <v>0.68</v>
       </c>
       <c r="AF85">
         <v>0</v>
       </c>
       <c r="AG85">
-        <v>715500</v>
+        <v>224400</v>
       </c>
       <c r="AH85">
-        <v>715500</v>
+        <v>224400</v>
       </c>
       <c r="AI85">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AJ85">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AK85">
         <v>0</v>
@@ -7001,13 +7001,13 @@
         <v>73</v>
       </c>
       <c r="G86" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H86">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="I86" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J86">
         <v>1005</v>
@@ -7019,31 +7019,31 @@
         <v>31</v>
       </c>
       <c r="AB86">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC86" s="1">
         <v>0</v>
       </c>
       <c r="AD86">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE86">
-        <v>0.08</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AF86">
         <v>0</v>
       </c>
       <c r="AG86">
-        <v>26400</v>
+        <v>769500</v>
       </c>
       <c r="AH86">
-        <v>26400</v>
+        <v>769500</v>
       </c>
       <c r="AI86">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK86">
         <v>0</v>
@@ -7087,13 +7087,13 @@
         <v>31</v>
       </c>
       <c r="AB87">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC87" s="1">
         <v>0</v>
       </c>
       <c r="AD87">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE87">
         <v>0.08</v>
@@ -7102,10 +7102,10 @@
         <v>0</v>
       </c>
       <c r="AG87">
-        <v>27000</v>
+        <v>26400</v>
       </c>
       <c r="AH87">
-        <v>27000</v>
+        <v>26400</v>
       </c>
       <c r="AI87">
         <v>0</v>
@@ -7137,13 +7137,13 @@
         <v>73</v>
       </c>
       <c r="G88" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H88">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="I88" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J88">
         <v>1005</v>
@@ -7155,13 +7155,13 @@
         <v>31</v>
       </c>
       <c r="AB88">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC88" s="1">
         <v>0</v>
       </c>
       <c r="AD88">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE88">
         <v>0.08</v>
@@ -7170,16 +7170,16 @@
         <v>0</v>
       </c>
       <c r="AG88">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="AH88">
-        <v>26400</v>
+        <v>27000</v>
       </c>
       <c r="AI88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ88">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AK88">
         <v>0</v>
@@ -7223,31 +7223,31 @@
         <v>31</v>
       </c>
       <c r="AB89">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC89" s="1">
         <v>0</v>
       </c>
       <c r="AD89">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE89">
-        <v>0.2</v>
+        <v>0.08</v>
       </c>
       <c r="AF89">
         <v>0</v>
       </c>
       <c r="AG89">
-        <v>67500</v>
+        <v>26400</v>
       </c>
       <c r="AH89">
-        <v>67500</v>
+        <v>26400</v>
       </c>
       <c r="AI89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ89">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="AK89">
         <v>0</v>
@@ -7273,13 +7273,13 @@
         <v>73</v>
       </c>
       <c r="G90" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H90">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="I90" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="J90">
         <v>1005</v>
@@ -7291,31 +7291,31 @@
         <v>31</v>
       </c>
       <c r="AB90">
-        <v>395000</v>
+        <v>337500</v>
       </c>
       <c r="AC90" s="1">
         <v>0</v>
       </c>
       <c r="AD90">
-        <v>395000</v>
+        <v>337500</v>
       </c>
       <c r="AE90">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="AF90">
         <v>0</v>
       </c>
       <c r="AG90">
-        <v>158000</v>
+        <v>67500</v>
       </c>
       <c r="AH90">
-        <v>158000</v>
+        <v>67500</v>
       </c>
       <c r="AI90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK90">
         <v>0</v>
@@ -7359,31 +7359,31 @@
         <v>31</v>
       </c>
       <c r="AB91">
-        <v>402500</v>
+        <v>395000</v>
       </c>
       <c r="AC91" s="1">
         <v>0</v>
       </c>
       <c r="AD91">
-        <v>402500</v>
+        <v>395000</v>
       </c>
       <c r="AE91">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AF91">
         <v>0</v>
       </c>
       <c r="AG91">
-        <v>402500</v>
+        <v>158000</v>
       </c>
       <c r="AH91">
-        <v>402500</v>
+        <v>158000</v>
       </c>
       <c r="AI91">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ91">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AK91">
         <v>0</v>
@@ -7409,49 +7409,49 @@
         <v>73</v>
       </c>
       <c r="G92" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H92">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="I92" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="J92">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K92" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L92" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB92">
-        <v>330000</v>
+        <v>402500</v>
       </c>
       <c r="AC92" s="1">
         <v>0</v>
       </c>
       <c r="AD92">
-        <v>330000</v>
+        <v>402500</v>
       </c>
       <c r="AE92">
-        <v>0.16</v>
+        <v>1.036</v>
       </c>
       <c r="AF92">
         <v>0</v>
       </c>
       <c r="AG92">
-        <v>52800</v>
+        <v>416990</v>
       </c>
       <c r="AH92">
-        <v>52800</v>
+        <v>416990</v>
       </c>
       <c r="AI92">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ92">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AK92">
         <v>0</v>
@@ -7495,31 +7495,31 @@
         <v>35</v>
       </c>
       <c r="AB93">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC93" s="1">
         <v>0</v>
       </c>
       <c r="AD93">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE93">
-        <v>4.74</v>
+        <v>0.32</v>
       </c>
       <c r="AF93">
         <v>0</v>
       </c>
       <c r="AG93">
-        <v>1599750</v>
+        <v>105600</v>
       </c>
       <c r="AH93">
-        <v>1599750</v>
+        <v>105600</v>
       </c>
       <c r="AI93">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ93">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="AK93">
         <v>0</v>
@@ -7545,13 +7545,13 @@
         <v>73</v>
       </c>
       <c r="G94" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H94">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="I94" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="J94">
         <v>1003</v>
@@ -7572,22 +7572,22 @@
         <v>337500</v>
       </c>
       <c r="AE94">
-        <v>0.68</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="AF94">
         <v>0</v>
       </c>
       <c r="AG94">
-        <v>229500</v>
+        <v>1694250</v>
       </c>
       <c r="AH94">
-        <v>229500</v>
+        <v>1694250</v>
       </c>
       <c r="AI94">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AJ94">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="AK94">
         <v>0</v>
@@ -7613,22 +7613,22 @@
         <v>73</v>
       </c>
       <c r="G95" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H95">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="I95" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J95">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K95" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L95" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AB95">
         <v>330000</v>
@@ -7640,22 +7640,22 @@
         <v>330000</v>
       </c>
       <c r="AE95">
-        <v>0.28000000000000003</v>
+        <v>0.04</v>
       </c>
       <c r="AF95">
         <v>0</v>
       </c>
       <c r="AG95">
-        <v>92400</v>
+        <v>13200</v>
       </c>
       <c r="AH95">
-        <v>92400</v>
+        <v>13200</v>
       </c>
       <c r="AI95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ95">
-        <v>0.28000000000000003</v>
+        <v>0</v>
       </c>
       <c r="AK95">
         <v>0</v>
@@ -7681,22 +7681,22 @@
         <v>73</v>
       </c>
       <c r="G96" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H96">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="I96" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="J96">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K96" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L96" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AB96">
         <v>337500</v>
@@ -7708,22 +7708,22 @@
         <v>337500</v>
       </c>
       <c r="AE96">
-        <v>1.2</v>
+        <v>0.84</v>
       </c>
       <c r="AF96">
         <v>0</v>
       </c>
       <c r="AG96">
-        <v>405000</v>
+        <v>283500</v>
       </c>
       <c r="AH96">
-        <v>405000</v>
+        <v>283500</v>
       </c>
       <c r="AI96">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AJ96">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="AK96">
         <v>0</v>
@@ -7749,13 +7749,13 @@
         <v>73</v>
       </c>
       <c r="G97" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="H97">
-        <v>10009</v>
+        <v>10007</v>
       </c>
       <c r="I97" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="J97">
         <v>1004</v>
@@ -7767,31 +7767,31 @@
         <v>41</v>
       </c>
       <c r="AB97">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC97" s="1">
         <v>0</v>
       </c>
       <c r="AD97">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE97">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="AF97">
         <v>0</v>
       </c>
       <c r="AG97">
-        <v>81000</v>
+        <v>158400</v>
       </c>
       <c r="AH97">
-        <v>81000</v>
+        <v>158400</v>
       </c>
       <c r="AI97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ97">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="AK97">
         <v>0</v>
@@ -7817,49 +7817,49 @@
         <v>73</v>
       </c>
       <c r="G98" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="H98">
-        <v>10010</v>
+        <v>10007</v>
       </c>
       <c r="I98" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J98">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K98" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L98" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AB98">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC98" s="1">
         <v>0</v>
       </c>
       <c r="AD98">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE98">
-        <v>0.18</v>
+        <v>1.36</v>
       </c>
       <c r="AF98">
         <v>0</v>
       </c>
       <c r="AG98">
-        <v>72450</v>
+        <v>459000</v>
       </c>
       <c r="AH98">
-        <v>72450</v>
+        <v>459000</v>
       </c>
       <c r="AI98">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK98">
         <v>0</v>
@@ -7885,49 +7885,49 @@
         <v>73</v>
       </c>
       <c r="G99" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H99">
-        <v>11005</v>
+        <v>10009</v>
       </c>
       <c r="I99" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="J99">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="K99" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L99" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AB99">
-        <v>205000</v>
+        <v>330000</v>
       </c>
       <c r="AC99" s="1">
         <v>0</v>
       </c>
       <c r="AD99">
-        <v>205000</v>
+        <v>330000</v>
       </c>
       <c r="AE99">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="AF99">
         <v>0</v>
       </c>
       <c r="AG99">
-        <v>45100</v>
+        <v>26400</v>
       </c>
       <c r="AH99">
-        <v>45100</v>
+        <v>26400</v>
       </c>
       <c r="AI99">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ99">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AK99">
         <v>0</v>
@@ -7944,52 +7944,52 @@
         <v>25</v>
       </c>
       <c r="D100" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E100">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F100" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G100" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H100">
-        <v>10001</v>
+        <v>10009</v>
       </c>
       <c r="I100" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J100">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K100" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L100" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB100">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC100" s="1">
         <v>0</v>
       </c>
       <c r="AD100">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE100">
-        <v>0.08</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF100">
         <v>0</v>
       </c>
       <c r="AG100">
-        <v>26400</v>
+        <v>94500</v>
       </c>
       <c r="AH100">
-        <v>26400</v>
+        <v>94500</v>
       </c>
       <c r="AI100">
         <v>0</v>
@@ -8012,31 +8012,31 @@
         <v>25</v>
       </c>
       <c r="D101" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E101">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F101" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G101" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H101">
-        <v>10004</v>
+        <v>10010</v>
       </c>
       <c r="I101" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J101">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB101">
         <v>402500</v>
@@ -8048,22 +8048,22 @@
         <v>402500</v>
       </c>
       <c r="AE101">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="AF101">
         <v>0</v>
       </c>
       <c r="AG101">
-        <v>48300</v>
+        <v>104650</v>
       </c>
       <c r="AH101">
-        <v>48300</v>
+        <v>104650</v>
       </c>
       <c r="AI101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ101">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="AK101">
         <v>0</v>
@@ -8080,58 +8080,58 @@
         <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E102">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F102" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G102" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H102">
-        <v>10005</v>
+        <v>11005</v>
       </c>
       <c r="I102" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J102">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K102" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L102" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB102">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AC102" s="1">
         <v>0</v>
       </c>
       <c r="AD102">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AE102">
-        <v>0.2</v>
+        <v>0.30399999999999999</v>
       </c>
       <c r="AF102">
         <v>0</v>
       </c>
       <c r="AG102">
-        <v>66000</v>
+        <v>62320</v>
       </c>
       <c r="AH102">
-        <v>66000</v>
+        <v>62320</v>
       </c>
       <c r="AI102">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="AK102">
         <v>0</v>
@@ -8157,49 +8157,49 @@
         <v>75</v>
       </c>
       <c r="G103" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H103">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I103" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J103">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K103" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L103" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB103">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC103" s="1">
         <v>0</v>
       </c>
       <c r="AD103">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE103">
-        <v>1.36</v>
+        <v>0.08</v>
       </c>
       <c r="AF103">
         <v>0</v>
       </c>
       <c r="AG103">
-        <v>459000</v>
+        <v>26400</v>
       </c>
       <c r="AH103">
-        <v>459000</v>
+        <v>26400</v>
       </c>
       <c r="AI103">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AJ103">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="AK103">
         <v>0</v>
@@ -8225,22 +8225,22 @@
         <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H104">
-        <v>10007</v>
+        <v>10001</v>
       </c>
       <c r="I104" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J104">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K104" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L104" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB104">
         <v>337500</v>
@@ -8293,46 +8293,46 @@
         <v>75</v>
       </c>
       <c r="G105" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="H105">
-        <v>10009</v>
+        <v>10004</v>
       </c>
       <c r="I105" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="J105">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K105" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L105" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB105">
-        <v>330000</v>
+        <v>402500</v>
       </c>
       <c r="AC105" s="1">
         <v>0</v>
       </c>
       <c r="AD105">
-        <v>330000</v>
+        <v>402500</v>
       </c>
       <c r="AE105">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="AF105">
         <v>0</v>
       </c>
       <c r="AG105">
-        <v>26400</v>
+        <v>96600</v>
       </c>
       <c r="AH105">
-        <v>26400</v>
+        <v>96600</v>
       </c>
       <c r="AI105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ105">
         <v>0.08</v>
@@ -8361,13 +8361,13 @@
         <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H106">
-        <v>10010</v>
+        <v>10005</v>
       </c>
       <c r="I106" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J106">
         <v>1003</v>
@@ -8379,31 +8379,31 @@
         <v>35</v>
       </c>
       <c r="AB106">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AC106" s="1">
         <v>0</v>
       </c>
       <c r="AD106">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AE106">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AF106">
         <v>0</v>
       </c>
       <c r="AG106">
-        <v>16100</v>
+        <v>66000</v>
       </c>
       <c r="AH106">
-        <v>16100</v>
+        <v>66000</v>
       </c>
       <c r="AI106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ106">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AK106">
         <v>0</v>
@@ -8429,49 +8429,49 @@
         <v>75</v>
       </c>
       <c r="G107" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H107">
-        <v>11005</v>
+        <v>10005</v>
       </c>
       <c r="I107" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J107">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="K107" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L107" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB107">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AC107" s="1">
         <v>0</v>
       </c>
       <c r="AD107">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AE107">
-        <v>0.44</v>
+        <v>1.68</v>
       </c>
       <c r="AF107">
         <v>0</v>
       </c>
       <c r="AG107">
-        <v>90200</v>
+        <v>567000</v>
       </c>
       <c r="AH107">
-        <v>90200</v>
+        <v>567000</v>
       </c>
       <c r="AI107">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AJ107">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AK107">
         <v>0</v>
@@ -8488,31 +8488,31 @@
         <v>25</v>
       </c>
       <c r="D108" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E108">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="H108">
-        <v>10001</v>
+        <v>10007</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J108">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K108" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L108" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB108">
         <v>337500</v>
@@ -8524,22 +8524,22 @@
         <v>337500</v>
       </c>
       <c r="AE108">
-        <v>2.84</v>
+        <v>0.2</v>
       </c>
       <c r="AF108">
         <v>0</v>
       </c>
       <c r="AG108">
-        <v>958500</v>
+        <v>67500</v>
       </c>
       <c r="AH108">
-        <v>958500</v>
+        <v>67500</v>
       </c>
       <c r="AI108">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AJ108">
-        <v>0.28000000000000003</v>
+        <v>0.04</v>
       </c>
       <c r="AK108">
         <v>0</v>
@@ -8556,58 +8556,58 @@
         <v>25</v>
       </c>
       <c r="D109" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E109">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="H109">
-        <v>10002</v>
+        <v>10008</v>
       </c>
       <c r="I109" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="J109">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K109" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L109" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB109">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AC109" s="1">
         <v>0</v>
       </c>
       <c r="AD109">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AE109">
-        <v>0.28000000000000003</v>
+        <v>0.04</v>
       </c>
       <c r="AF109">
         <v>0</v>
       </c>
       <c r="AG109">
-        <v>94500</v>
+        <v>9500</v>
       </c>
       <c r="AH109">
-        <v>94500</v>
+        <v>9500</v>
       </c>
       <c r="AI109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ109">
-        <v>0.14000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="AK109">
         <v>0</v>
@@ -8624,58 +8624,58 @@
         <v>25</v>
       </c>
       <c r="D110" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E110">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H110">
-        <v>10003</v>
+        <v>10009</v>
       </c>
       <c r="I110" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J110">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K110" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L110" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB110">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC110" s="1">
         <v>0</v>
       </c>
       <c r="AD110">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE110">
-        <v>0.32</v>
+        <v>0.08</v>
       </c>
       <c r="AF110">
         <v>0</v>
       </c>
       <c r="AG110">
-        <v>108000</v>
+        <v>26400</v>
       </c>
       <c r="AH110">
-        <v>108000</v>
+        <v>26400</v>
       </c>
       <c r="AI110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ110">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="AK110">
         <v>0</v>
@@ -8692,31 +8692,31 @@
         <v>25</v>
       </c>
       <c r="D111" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E111">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G111" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H111">
-        <v>10004</v>
+        <v>10010</v>
       </c>
       <c r="I111" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J111">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K111" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L111" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB111">
         <v>402500</v>
@@ -8728,22 +8728,22 @@
         <v>402500</v>
       </c>
       <c r="AE111">
-        <v>0.84</v>
+        <v>0.04</v>
       </c>
       <c r="AF111">
         <v>0</v>
       </c>
       <c r="AG111">
-        <v>338100</v>
+        <v>16100</v>
       </c>
       <c r="AH111">
-        <v>338100</v>
+        <v>16100</v>
       </c>
       <c r="AI111">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AJ111">
-        <v>0.21</v>
+        <v>0.04</v>
       </c>
       <c r="AK111">
         <v>0</v>
@@ -8760,58 +8760,58 @@
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E112">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="G112" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H112">
-        <v>10005</v>
+        <v>11005</v>
       </c>
       <c r="I112" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J112">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K112" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L112" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB112">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AC112" s="1">
         <v>0</v>
       </c>
       <c r="AD112">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AE112">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="AF112">
         <v>0</v>
       </c>
       <c r="AG112">
-        <v>330000</v>
+        <v>90200</v>
       </c>
       <c r="AH112">
-        <v>330000</v>
+        <v>90200</v>
       </c>
       <c r="AI112">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AK112">
         <v>0</v>
@@ -8837,22 +8837,22 @@
         <v>77</v>
       </c>
       <c r="G113" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H113">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I113" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J113">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K113" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L113" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB113">
         <v>337500</v>
@@ -8864,22 +8864,22 @@
         <v>337500</v>
       </c>
       <c r="AE113">
-        <v>2.44</v>
+        <v>2.84</v>
       </c>
       <c r="AF113">
         <v>0</v>
       </c>
       <c r="AG113">
-        <v>823500</v>
+        <v>958500</v>
       </c>
       <c r="AH113">
-        <v>823500</v>
+        <v>958500</v>
       </c>
       <c r="AI113">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ113">
-        <v>0.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AK113">
         <v>0</v>
@@ -8905,22 +8905,22 @@
         <v>77</v>
       </c>
       <c r="G114" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H114">
-        <v>10006</v>
+        <v>10002</v>
       </c>
       <c r="I114" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J114">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K114" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L114" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB114">
         <v>337500</v>
@@ -8932,22 +8932,22 @@
         <v>337500</v>
       </c>
       <c r="AE114">
-        <v>0.08</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF114">
         <v>0</v>
       </c>
       <c r="AG114">
-        <v>27000</v>
+        <v>94500</v>
       </c>
       <c r="AH114">
-        <v>27000</v>
+        <v>94500</v>
       </c>
       <c r="AI114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK114">
         <v>0</v>
@@ -8973,22 +8973,22 @@
         <v>77</v>
       </c>
       <c r="G115" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H115">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="I115" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J115">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K115" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L115" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB115">
         <v>337500</v>
@@ -9000,22 +9000,22 @@
         <v>337500</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>0.32</v>
       </c>
       <c r="AF115">
         <v>0</v>
       </c>
       <c r="AG115">
-        <v>364500</v>
+        <v>108000</v>
       </c>
       <c r="AH115">
-        <v>364500</v>
+        <v>108000</v>
       </c>
       <c r="AI115">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AJ115">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="AK115">
         <v>0</v>
@@ -9041,49 +9041,49 @@
         <v>77</v>
       </c>
       <c r="G116" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H116">
-        <v>10008</v>
+        <v>10004</v>
       </c>
       <c r="I116" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J116">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K116" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L116" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB116">
-        <v>237500</v>
+        <v>402500</v>
       </c>
       <c r="AC116" s="1">
         <v>0</v>
       </c>
       <c r="AD116">
-        <v>237500</v>
+        <v>402500</v>
       </c>
       <c r="AE116">
-        <v>0.02</v>
+        <v>0.84</v>
       </c>
       <c r="AF116">
         <v>0</v>
       </c>
       <c r="AG116">
-        <v>4750</v>
+        <v>338100</v>
       </c>
       <c r="AH116">
-        <v>4750</v>
+        <v>338100</v>
       </c>
       <c r="AI116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="AK116">
         <v>0</v>
@@ -9109,13 +9109,13 @@
         <v>77</v>
       </c>
       <c r="G117" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="H117">
-        <v>10010</v>
+        <v>10005</v>
       </c>
       <c r="I117" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="J117">
         <v>1003</v>
@@ -9127,31 +9127,31 @@
         <v>35</v>
       </c>
       <c r="AB117">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AC117" s="1">
         <v>0</v>
       </c>
       <c r="AD117">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AE117">
-        <v>0.38</v>
+        <v>1</v>
       </c>
       <c r="AF117">
         <v>0</v>
       </c>
       <c r="AG117">
-        <v>152950</v>
+        <v>330000</v>
       </c>
       <c r="AH117">
-        <v>152950</v>
+        <v>330000</v>
       </c>
       <c r="AI117">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ117">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="AK117">
         <v>0</v>
@@ -9177,49 +9177,49 @@
         <v>77</v>
       </c>
       <c r="G118" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H118">
-        <v>11005</v>
+        <v>10005</v>
       </c>
       <c r="I118" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J118">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="K118" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L118" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB118">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AC118" s="1">
         <v>0</v>
       </c>
       <c r="AD118">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AE118">
-        <v>2.2000000000000002</v>
+        <v>2.44</v>
       </c>
       <c r="AF118">
         <v>0</v>
       </c>
       <c r="AG118">
-        <v>451000</v>
+        <v>823500</v>
       </c>
       <c r="AH118">
-        <v>451000</v>
+        <v>823500</v>
       </c>
       <c r="AI118">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AJ118">
-        <v>0.14000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="AK118">
         <v>0</v>
@@ -9236,31 +9236,31 @@
         <v>25</v>
       </c>
       <c r="D119" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E119">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F119" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G119" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H119">
-        <v>10001</v>
+        <v>10006</v>
       </c>
       <c r="I119" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J119">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K119" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L119" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB119">
         <v>337500</v>
@@ -9304,58 +9304,58 @@
         <v>25</v>
       </c>
       <c r="D120" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E120">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F120" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G120" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H120">
-        <v>10004</v>
+        <v>10007</v>
       </c>
       <c r="I120" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J120">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K120" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L120" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB120">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC120" s="1">
         <v>0</v>
       </c>
       <c r="AD120">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE120">
-        <v>0.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
         <v>0</v>
       </c>
       <c r="AG120">
-        <v>16100</v>
+        <v>364500</v>
       </c>
       <c r="AH120">
-        <v>16100</v>
+        <v>364500</v>
       </c>
       <c r="AI120">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ120">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AK120">
         <v>0</v>
@@ -9372,58 +9372,58 @@
         <v>25</v>
       </c>
       <c r="D121" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E121">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F121" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G121" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H121">
-        <v>10005</v>
+        <v>10008</v>
       </c>
       <c r="I121" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="J121">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K121" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L121" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB121">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AC121" s="1">
         <v>0</v>
       </c>
       <c r="AD121">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AE121">
-        <v>9.4480000000000004</v>
+        <v>0.02</v>
       </c>
       <c r="AF121">
         <v>0</v>
       </c>
       <c r="AG121">
-        <v>3188700</v>
+        <v>4750</v>
       </c>
       <c r="AH121">
-        <v>3188700</v>
+        <v>4750</v>
       </c>
       <c r="AI121">
-        <v>121</v>
+        <v>0</v>
       </c>
       <c r="AJ121">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AK121">
         <v>0</v>
@@ -9440,58 +9440,58 @@
         <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E122">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F122" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G122" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H122">
-        <v>10007</v>
+        <v>10010</v>
       </c>
       <c r="I122" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="J122">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="K122" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L122" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AB122">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AC122" s="1">
         <v>0</v>
       </c>
       <c r="AD122">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AE122">
-        <v>0.04</v>
+        <v>0.38</v>
       </c>
       <c r="AF122">
         <v>0</v>
       </c>
       <c r="AG122">
-        <v>13500</v>
+        <v>152950</v>
       </c>
       <c r="AH122">
-        <v>13500</v>
+        <v>152950</v>
       </c>
       <c r="AI122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ122">
-        <v>0.04</v>
+        <v>0.19</v>
       </c>
       <c r="AK122">
         <v>0</v>
@@ -9508,58 +9508,58 @@
         <v>25</v>
       </c>
       <c r="D123" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E123">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F123" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G123" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H123">
-        <v>10001</v>
+        <v>11005</v>
       </c>
       <c r="I123" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="J123">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K123" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L123" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB123">
-        <v>333750</v>
+        <v>205000</v>
       </c>
       <c r="AC123" s="1">
         <v>0</v>
       </c>
       <c r="AD123">
-        <v>333750</v>
+        <v>205000</v>
       </c>
       <c r="AE123">
-        <v>2</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="AF123">
         <v>0</v>
       </c>
       <c r="AG123">
-        <v>667500</v>
+        <v>451000</v>
       </c>
       <c r="AH123">
-        <v>667500</v>
+        <v>451000</v>
       </c>
       <c r="AI123">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AJ123">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK123">
         <v>0</v>
@@ -9576,13 +9576,13 @@
         <v>25</v>
       </c>
       <c r="D124" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E124">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F124" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s">
         <v>52</v>
@@ -9612,22 +9612,22 @@
         <v>337500</v>
       </c>
       <c r="AE124">
-        <v>2.08</v>
+        <v>0.08</v>
       </c>
       <c r="AF124">
         <v>0</v>
       </c>
       <c r="AG124">
-        <v>702000</v>
+        <v>27000</v>
       </c>
       <c r="AH124">
-        <v>702000</v>
+        <v>27000</v>
       </c>
       <c r="AI124">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ124">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="AK124">
         <v>0</v>
@@ -9644,22 +9644,22 @@
         <v>25</v>
       </c>
       <c r="D125" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E125">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F125" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G125" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="H125">
-        <v>10002</v>
+        <v>10004</v>
       </c>
       <c r="I125" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="J125">
         <v>1005</v>
@@ -9671,31 +9671,31 @@
         <v>31</v>
       </c>
       <c r="AB125">
-        <v>333750</v>
+        <v>402500</v>
       </c>
       <c r="AC125" s="1">
         <v>0</v>
       </c>
       <c r="AD125">
-        <v>333750</v>
+        <v>402500</v>
       </c>
       <c r="AE125">
-        <v>1</v>
+        <v>0.04</v>
       </c>
       <c r="AF125">
         <v>0</v>
       </c>
       <c r="AG125">
-        <v>333750</v>
+        <v>16100</v>
       </c>
       <c r="AH125">
-        <v>333750</v>
+        <v>16100</v>
       </c>
       <c r="AI125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ125">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AK125">
         <v>0</v>
@@ -9712,31 +9712,31 @@
         <v>25</v>
       </c>
       <c r="D126" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E126">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G126" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H126">
-        <v>10002</v>
+        <v>10005</v>
       </c>
       <c r="I126" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J126">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB126">
         <v>337500</v>
@@ -9748,22 +9748,22 @@
         <v>337500</v>
       </c>
       <c r="AE126">
-        <v>0.12</v>
+        <v>13.448</v>
       </c>
       <c r="AF126">
         <v>0</v>
       </c>
       <c r="AG126">
-        <v>40500</v>
+        <v>4538700</v>
       </c>
       <c r="AH126">
-        <v>40500</v>
+        <v>4538700</v>
       </c>
       <c r="AI126">
-        <v>3</v>
+        <v>143</v>
       </c>
       <c r="AJ126">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="AK126">
         <v>0</v>
@@ -9780,31 +9780,31 @@
         <v>25</v>
       </c>
       <c r="D127" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E127">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F127" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G127" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H127">
-        <v>10003</v>
+        <v>10007</v>
       </c>
       <c r="I127" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="J127">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K127" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L127" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB127">
         <v>337500</v>
@@ -9816,22 +9816,22 @@
         <v>337500</v>
       </c>
       <c r="AE127">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AF127">
         <v>0</v>
       </c>
       <c r="AG127">
-        <v>27000</v>
+        <v>13500</v>
       </c>
       <c r="AH127">
-        <v>27000</v>
+        <v>13500</v>
       </c>
       <c r="AI127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ127">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AK127">
         <v>0</v>
@@ -9848,58 +9848,58 @@
         <v>25</v>
       </c>
       <c r="D128" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E128">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F128" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H128">
-        <v>10004</v>
+        <v>10010</v>
       </c>
       <c r="I128" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J128">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L128" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB128">
-        <v>398750</v>
+        <v>402500</v>
       </c>
       <c r="AC128" s="1">
         <v>0</v>
       </c>
       <c r="AD128">
-        <v>398750</v>
+        <v>402500</v>
       </c>
       <c r="AE128">
-        <v>1.6</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="AF128">
         <v>0</v>
       </c>
       <c r="AG128">
-        <v>638000</v>
+        <v>225400</v>
       </c>
       <c r="AH128">
-        <v>638000</v>
+        <v>225400</v>
       </c>
       <c r="AI128">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ128">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK128">
         <v>0</v>
@@ -9925,13 +9925,13 @@
         <v>81</v>
       </c>
       <c r="G129" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="H129">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="I129" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="J129">
         <v>1005</v>
@@ -9943,31 +9943,31 @@
         <v>31</v>
       </c>
       <c r="AB129">
-        <v>402500</v>
+        <v>333750</v>
       </c>
       <c r="AC129" s="1">
         <v>0</v>
       </c>
       <c r="AD129">
-        <v>402500</v>
+        <v>333750</v>
       </c>
       <c r="AE129">
-        <v>0.64</v>
+        <v>2</v>
       </c>
       <c r="AF129">
         <v>0</v>
       </c>
       <c r="AG129">
-        <v>257600</v>
+        <v>667500</v>
       </c>
       <c r="AH129">
-        <v>257600</v>
+        <v>667500</v>
       </c>
       <c r="AI129">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ129">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AK129">
         <v>0</v>
@@ -9993,49 +9993,49 @@
         <v>81</v>
       </c>
       <c r="G130" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H130">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I130" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J130">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K130" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L130" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB130">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AC130" s="1">
         <v>0</v>
       </c>
       <c r="AD130">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AE130">
-        <v>4</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="AF130">
         <v>0</v>
       </c>
       <c r="AG130">
-        <v>1335000</v>
+        <v>769500</v>
       </c>
       <c r="AH130">
-        <v>1335000</v>
+        <v>769500</v>
       </c>
       <c r="AI130">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="AJ130">
-        <v>4</v>
+        <v>0.18</v>
       </c>
       <c r="AK130">
         <v>0</v>
@@ -10061,49 +10061,49 @@
         <v>81</v>
       </c>
       <c r="G131" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H131">
-        <v>10005</v>
+        <v>10002</v>
       </c>
       <c r="I131" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="J131">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K131" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L131" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB131">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC131" s="1">
         <v>0</v>
       </c>
       <c r="AD131">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE131">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AF131">
         <v>0</v>
       </c>
       <c r="AG131">
-        <v>540000</v>
+        <v>333750</v>
       </c>
       <c r="AH131">
-        <v>540000</v>
+        <v>333750</v>
       </c>
       <c r="AI131">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ131">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="AK131">
         <v>0</v>
@@ -10129,22 +10129,22 @@
         <v>81</v>
       </c>
       <c r="G132" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H132">
-        <v>10007</v>
+        <v>10002</v>
       </c>
       <c r="I132" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="J132">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K132" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L132" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB132">
         <v>337500</v>
@@ -10156,19 +10156,19 @@
         <v>337500</v>
       </c>
       <c r="AE132">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="AF132">
         <v>0</v>
       </c>
       <c r="AG132">
-        <v>13500</v>
+        <v>40500</v>
       </c>
       <c r="AH132">
-        <v>13500</v>
+        <v>40500</v>
       </c>
       <c r="AI132">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ132">
         <v>0.04</v>
@@ -10197,49 +10197,49 @@
         <v>81</v>
       </c>
       <c r="G133" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H133">
-        <v>10008</v>
+        <v>10003</v>
       </c>
       <c r="I133" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J133">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K133" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L133" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB133">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AC133" s="1">
         <v>0</v>
       </c>
       <c r="AD133">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AE133">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="AF133">
         <v>0</v>
       </c>
       <c r="AG133">
-        <v>38000</v>
+        <v>27000</v>
       </c>
       <c r="AH133">
-        <v>38000</v>
+        <v>27000</v>
       </c>
       <c r="AI133">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ133">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="AK133">
         <v>0</v>
@@ -10265,43 +10265,43 @@
         <v>81</v>
       </c>
       <c r="G134" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="H134">
-        <v>10009</v>
+        <v>10004</v>
       </c>
       <c r="I134" t="s">
-        <v>61</v>
+        <v>29</v>
       </c>
       <c r="J134">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K134" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L134" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB134">
-        <v>337500</v>
+        <v>398750</v>
       </c>
       <c r="AC134" s="1">
         <v>0</v>
       </c>
       <c r="AD134">
-        <v>337500</v>
+        <v>398750</v>
       </c>
       <c r="AE134">
-        <v>0.08</v>
+        <v>1.6</v>
       </c>
       <c r="AF134">
         <v>0</v>
       </c>
       <c r="AG134">
-        <v>27000</v>
+        <v>638000</v>
       </c>
       <c r="AH134">
-        <v>27000</v>
+        <v>638000</v>
       </c>
       <c r="AI134">
         <v>0</v>
@@ -10333,49 +10333,49 @@
         <v>81</v>
       </c>
       <c r="G135" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H135">
-        <v>11005</v>
+        <v>10004</v>
       </c>
       <c r="I135" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J135">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K135" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L135" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB135">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AC135" s="1">
         <v>0</v>
       </c>
       <c r="AD135">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AE135">
-        <v>1.6</v>
+        <v>0.64</v>
       </c>
       <c r="AF135">
         <v>0</v>
       </c>
       <c r="AG135">
-        <v>328000</v>
+        <v>257600</v>
       </c>
       <c r="AH135">
-        <v>328000</v>
+        <v>257600</v>
       </c>
       <c r="AI135">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ135">
-        <v>0.53</v>
+        <v>0.11</v>
       </c>
       <c r="AK135">
         <v>0</v>
@@ -10392,58 +10392,58 @@
         <v>25</v>
       </c>
       <c r="D136" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E136">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G136" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H136">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I136" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J136">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K136" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L136" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB136">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC136" s="1">
         <v>0</v>
       </c>
       <c r="AD136">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE136">
-        <v>0.72</v>
+        <v>4</v>
       </c>
       <c r="AF136">
         <v>0</v>
       </c>
       <c r="AG136">
-        <v>243000</v>
+        <v>1335000</v>
       </c>
       <c r="AH136">
-        <v>243000</v>
+        <v>1335000</v>
       </c>
       <c r="AI136">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ136">
-        <v>0.1</v>
+        <v>4</v>
       </c>
       <c r="AK136">
         <v>0</v>
@@ -10460,31 +10460,31 @@
         <v>25</v>
       </c>
       <c r="D137" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E137">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F137" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G137" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H137">
-        <v>10002</v>
+        <v>10005</v>
       </c>
       <c r="I137" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J137">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K137" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L137" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB137">
         <v>337500</v>
@@ -10496,22 +10496,22 @@
         <v>337500</v>
       </c>
       <c r="AE137">
-        <v>0.04</v>
+        <v>1.76</v>
       </c>
       <c r="AF137">
         <v>0</v>
       </c>
       <c r="AG137">
-        <v>13500</v>
+        <v>594000</v>
       </c>
       <c r="AH137">
-        <v>13500</v>
+        <v>594000</v>
       </c>
       <c r="AI137">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ137">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="AK137">
         <v>0</v>
@@ -10528,31 +10528,31 @@
         <v>25</v>
       </c>
       <c r="D138" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E138">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F138" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G138" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H138">
-        <v>10003</v>
+        <v>10007</v>
       </c>
       <c r="I138" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="J138">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K138" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L138" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB138">
         <v>337500</v>
@@ -10576,10 +10576,10 @@
         <v>13500</v>
       </c>
       <c r="AI138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ138">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AK138">
         <v>0</v>
@@ -10596,58 +10596,58 @@
         <v>25</v>
       </c>
       <c r="D139" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E139">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G139" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H139">
-        <v>10004</v>
+        <v>10008</v>
       </c>
       <c r="I139" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J139">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K139" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L139" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB139">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AC139" s="1">
         <v>0</v>
       </c>
       <c r="AD139">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AE139">
-        <v>0.44</v>
+        <v>0.16</v>
       </c>
       <c r="AF139">
         <v>0</v>
       </c>
       <c r="AG139">
-        <v>177100</v>
+        <v>38000</v>
       </c>
       <c r="AH139">
-        <v>177100</v>
+        <v>38000</v>
       </c>
       <c r="AI139">
         <v>1</v>
       </c>
       <c r="AJ139">
-        <v>0.44</v>
+        <v>0.16</v>
       </c>
       <c r="AK139">
         <v>0</v>
@@ -10664,31 +10664,31 @@
         <v>25</v>
       </c>
       <c r="D140" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E140">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F140" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G140" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="H140">
-        <v>10005</v>
+        <v>10009</v>
       </c>
       <c r="I140" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="J140">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K140" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L140" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AB140">
         <v>337500</v>
@@ -10700,22 +10700,22 @@
         <v>337500</v>
       </c>
       <c r="AE140">
-        <v>1.52</v>
+        <v>0.08</v>
       </c>
       <c r="AF140">
         <v>0</v>
       </c>
       <c r="AG140">
-        <v>513000</v>
+        <v>27000</v>
       </c>
       <c r="AH140">
-        <v>513000</v>
+        <v>27000</v>
       </c>
       <c r="AI140">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AJ140">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK140">
         <v>0</v>
@@ -10732,58 +10732,58 @@
         <v>25</v>
       </c>
       <c r="D141" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E141">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F141" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G141" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="H141">
-        <v>10007</v>
+        <v>11005</v>
       </c>
       <c r="I141" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="J141">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="K141" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L141" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="AB141">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AC141" s="1">
         <v>0</v>
       </c>
       <c r="AD141">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AE141">
-        <v>0.16</v>
+        <v>1.56</v>
       </c>
       <c r="AF141">
         <v>0</v>
       </c>
       <c r="AG141">
-        <v>54000</v>
+        <v>319800</v>
       </c>
       <c r="AH141">
-        <v>54000</v>
+        <v>319800</v>
       </c>
       <c r="AI141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ141">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="AK141">
         <v>0</v>
@@ -10809,49 +10809,49 @@
         <v>83</v>
       </c>
       <c r="G142" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="H142">
-        <v>10010</v>
+        <v>10001</v>
       </c>
       <c r="I142" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J142">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K142" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L142" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB142">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC142" s="1">
         <v>0</v>
       </c>
       <c r="AD142">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE142">
-        <v>0.1</v>
+        <v>1.04</v>
       </c>
       <c r="AF142">
         <v>0</v>
       </c>
       <c r="AG142">
-        <v>40250</v>
+        <v>351000</v>
       </c>
       <c r="AH142">
-        <v>40250</v>
+        <v>351000</v>
       </c>
       <c r="AI142">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AJ142">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AK142">
         <v>0</v>
@@ -10877,49 +10877,49 @@
         <v>83</v>
       </c>
       <c r="G143" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H143">
-        <v>11005</v>
+        <v>10002</v>
       </c>
       <c r="I143" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="J143">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K143" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L143" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB143">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AC143" s="1">
         <v>0</v>
       </c>
       <c r="AD143">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AE143">
-        <v>0.6</v>
+        <v>0.04</v>
       </c>
       <c r="AF143">
         <v>0</v>
       </c>
       <c r="AG143">
-        <v>123000</v>
+        <v>13500</v>
       </c>
       <c r="AH143">
-        <v>123000</v>
+        <v>13500</v>
       </c>
       <c r="AI143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ143">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="AK143">
         <v>0</v>
@@ -10936,22 +10936,22 @@
         <v>25</v>
       </c>
       <c r="D144" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E144">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F144" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G144" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H144">
-        <v>10001</v>
+        <v>10003</v>
       </c>
       <c r="I144" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="J144">
         <v>1005</v>
@@ -10963,31 +10963,31 @@
         <v>31</v>
       </c>
       <c r="AB144">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC144" s="1">
         <v>0</v>
       </c>
       <c r="AD144">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE144">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
       <c r="AF144">
         <v>0</v>
       </c>
       <c r="AG144">
-        <v>52800</v>
+        <v>40500</v>
       </c>
       <c r="AH144">
-        <v>52800</v>
+        <v>40500</v>
       </c>
       <c r="AI144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ144">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK144">
         <v>0</v>
@@ -11004,22 +11004,22 @@
         <v>25</v>
       </c>
       <c r="D145" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E145">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F145" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G145" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="H145">
-        <v>10001</v>
+        <v>10004</v>
       </c>
       <c r="I145" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="J145">
         <v>1005</v>
@@ -11031,31 +11031,31 @@
         <v>31</v>
       </c>
       <c r="AB145">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AC145" s="1">
         <v>0</v>
       </c>
       <c r="AD145">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AE145">
-        <v>0.92</v>
+        <v>0.44</v>
       </c>
       <c r="AF145">
         <v>0</v>
       </c>
       <c r="AG145">
-        <v>310500</v>
+        <v>177100</v>
       </c>
       <c r="AH145">
-        <v>310500</v>
+        <v>177100</v>
       </c>
       <c r="AI145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ145">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="AK145">
         <v>0</v>
@@ -11072,58 +11072,58 @@
         <v>25</v>
       </c>
       <c r="D146" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E146">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F146" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G146" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H146">
-        <v>10002</v>
+        <v>10005</v>
       </c>
       <c r="I146" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="J146">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K146" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L146" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB146">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC146" s="1">
         <v>0</v>
       </c>
       <c r="AD146">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE146">
-        <v>0.04</v>
+        <v>1.8</v>
       </c>
       <c r="AF146">
         <v>0</v>
       </c>
       <c r="AG146">
-        <v>13200</v>
+        <v>607500</v>
       </c>
       <c r="AH146">
-        <v>13200</v>
+        <v>607500</v>
       </c>
       <c r="AI146">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AJ146">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="AK146">
         <v>0</v>
@@ -11140,58 +11140,58 @@
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E147">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F147" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G147" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H147">
-        <v>10004</v>
+        <v>10006</v>
       </c>
       <c r="I147" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J147">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K147" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L147" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB147">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC147" s="1">
         <v>0</v>
       </c>
       <c r="AD147">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE147">
-        <v>0.96</v>
+        <v>0.04</v>
       </c>
       <c r="AF147">
         <v>0</v>
       </c>
       <c r="AG147">
-        <v>386400</v>
+        <v>13500</v>
       </c>
       <c r="AH147">
-        <v>386400</v>
+        <v>13500</v>
       </c>
       <c r="AI147">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AJ147">
-        <v>0.11</v>
+        <v>0.04</v>
       </c>
       <c r="AK147">
         <v>0</v>
@@ -11208,58 +11208,58 @@
         <v>25</v>
       </c>
       <c r="D148" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E148">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F148" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G148" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H148">
-        <v>10005</v>
+        <v>10007</v>
       </c>
       <c r="I148" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="J148">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="K148" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="L148" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AB148">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC148" s="1">
         <v>0</v>
       </c>
       <c r="AD148">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE148">
-        <v>0.36</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF148">
         <v>0</v>
       </c>
       <c r="AG148">
-        <v>118800</v>
+        <v>94500</v>
       </c>
       <c r="AH148">
-        <v>118800</v>
+        <v>94500</v>
       </c>
       <c r="AI148">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ148">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK148">
         <v>0</v>
@@ -11276,22 +11276,22 @@
         <v>25</v>
       </c>
       <c r="D149" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E149">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F149" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G149" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H149">
-        <v>10005</v>
+        <v>10010</v>
       </c>
       <c r="I149" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J149">
         <v>1003</v>
@@ -11303,31 +11303,31 @@
         <v>35</v>
       </c>
       <c r="AB149">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AC149" s="1">
         <v>0</v>
       </c>
       <c r="AD149">
-        <v>337500</v>
+        <v>402500</v>
       </c>
       <c r="AE149">
-        <v>2.12</v>
+        <v>0.1</v>
       </c>
       <c r="AF149">
         <v>0</v>
       </c>
       <c r="AG149">
-        <v>715500</v>
+        <v>40250</v>
       </c>
       <c r="AH149">
-        <v>715500</v>
+        <v>40250</v>
       </c>
       <c r="AI149">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AJ149">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="AK149">
         <v>0</v>
@@ -11344,58 +11344,58 @@
         <v>25</v>
       </c>
       <c r="D150" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E150">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F150" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G150" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="H150">
-        <v>10006</v>
+        <v>11005</v>
       </c>
       <c r="I150" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="J150">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K150" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L150" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB150">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AC150" s="1">
         <v>0</v>
       </c>
       <c r="AD150">
-        <v>330000</v>
+        <v>205000</v>
       </c>
       <c r="AE150">
-        <v>0.04</v>
+        <v>0.8</v>
       </c>
       <c r="AF150">
         <v>0</v>
       </c>
       <c r="AG150">
-        <v>13200</v>
+        <v>164000</v>
       </c>
       <c r="AH150">
-        <v>13200</v>
+        <v>164000</v>
       </c>
       <c r="AI150">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ150">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK150">
         <v>0</v>
@@ -11421,49 +11421,49 @@
         <v>85</v>
       </c>
       <c r="G151" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H151">
-        <v>10006</v>
+        <v>10001</v>
       </c>
       <c r="I151" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J151">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K151" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L151" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB151">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC151" s="1">
         <v>0</v>
       </c>
       <c r="AD151">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE151">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
       <c r="AF151">
         <v>0</v>
       </c>
       <c r="AG151">
-        <v>81000</v>
+        <v>52800</v>
       </c>
       <c r="AH151">
-        <v>81000</v>
+        <v>52800</v>
       </c>
       <c r="AI151">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ151">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="AK151">
         <v>0</v>
@@ -11489,22 +11489,22 @@
         <v>85</v>
       </c>
       <c r="G152" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H152">
-        <v>10007</v>
+        <v>10001</v>
       </c>
       <c r="I152" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J152">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K152" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L152" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB152">
         <v>337500</v>
@@ -11516,22 +11516,22 @@
         <v>337500</v>
       </c>
       <c r="AE152">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="AF152">
         <v>0</v>
       </c>
       <c r="AG152">
-        <v>229500</v>
+        <v>324000</v>
       </c>
       <c r="AH152">
-        <v>229500</v>
+        <v>324000</v>
       </c>
       <c r="AI152">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AJ152">
-        <v>0.09</v>
+        <v>0.48</v>
       </c>
       <c r="AK152">
         <v>0</v>
@@ -11557,49 +11557,49 @@
         <v>85</v>
       </c>
       <c r="G153" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H153">
-        <v>10010</v>
+        <v>10002</v>
       </c>
       <c r="I153" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J153">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K153" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L153" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB153">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AC153" s="1">
         <v>0</v>
       </c>
       <c r="AD153">
-        <v>402500</v>
+        <v>330000</v>
       </c>
       <c r="AE153">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="AF153">
         <v>0</v>
       </c>
       <c r="AG153">
-        <v>48300</v>
+        <v>13200</v>
       </c>
       <c r="AH153">
-        <v>48300</v>
+        <v>13200</v>
       </c>
       <c r="AI153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ153">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="AK153">
         <v>0</v>
@@ -11625,49 +11625,49 @@
         <v>85</v>
       </c>
       <c r="G154" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H154">
-        <v>11005</v>
+        <v>10004</v>
       </c>
       <c r="I154" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J154">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K154" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L154" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB154">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AC154" s="1">
         <v>0</v>
       </c>
       <c r="AD154">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AE154">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="AF154">
         <v>0</v>
       </c>
       <c r="AG154">
-        <v>131200</v>
+        <v>386400</v>
       </c>
       <c r="AH154">
-        <v>131200</v>
+        <v>386400</v>
       </c>
       <c r="AI154">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ154">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="AK154">
         <v>0</v>
@@ -11684,52 +11684,52 @@
         <v>25</v>
       </c>
       <c r="D155" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E155">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F155" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G155" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H155">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I155" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J155">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K155" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L155" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB155">
-        <v>327500</v>
+        <v>330000</v>
       </c>
       <c r="AC155" s="1">
         <v>0</v>
       </c>
       <c r="AD155">
-        <v>327500</v>
+        <v>330000</v>
       </c>
       <c r="AE155">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="AF155">
         <v>0</v>
       </c>
       <c r="AG155">
-        <v>131000</v>
+        <v>118800</v>
       </c>
       <c r="AH155">
-        <v>131000</v>
+        <v>118800</v>
       </c>
       <c r="AI155">
         <v>0</v>
@@ -11752,58 +11752,58 @@
         <v>25</v>
       </c>
       <c r="D156" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E156">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F156" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G156" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H156">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I156" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J156">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K156" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L156" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB156">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC156" s="1">
         <v>0</v>
       </c>
       <c r="AD156">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE156">
-        <v>0.48</v>
+        <v>2.16</v>
       </c>
       <c r="AF156">
         <v>0</v>
       </c>
       <c r="AG156">
-        <v>158400</v>
+        <v>729000</v>
       </c>
       <c r="AH156">
-        <v>158400</v>
+        <v>729000</v>
       </c>
       <c r="AI156">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ156">
-        <v>0</v>
+        <v>0.36</v>
       </c>
       <c r="AK156">
         <v>0</v>
@@ -11820,58 +11820,58 @@
         <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E157">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F157" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G157" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="H157">
-        <v>10001</v>
+        <v>10006</v>
       </c>
       <c r="I157" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="J157">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K157" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L157" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB157">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC157" s="1">
         <v>0</v>
       </c>
       <c r="AD157">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE157">
-        <v>1.04</v>
+        <v>0.04</v>
       </c>
       <c r="AF157">
         <v>0</v>
       </c>
       <c r="AG157">
-        <v>351000</v>
+        <v>13200</v>
       </c>
       <c r="AH157">
-        <v>351000</v>
+        <v>13200</v>
       </c>
       <c r="AI157">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AJ157">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AK157">
         <v>0</v>
@@ -11888,58 +11888,58 @@
         <v>25</v>
       </c>
       <c r="D158" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E158">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F158" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G158" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H158">
-        <v>10004</v>
+        <v>10006</v>
       </c>
       <c r="I158" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="J158">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K158" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L158" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB158">
-        <v>392500</v>
+        <v>337500</v>
       </c>
       <c r="AC158" s="1">
         <v>0</v>
       </c>
       <c r="AD158">
-        <v>392500</v>
+        <v>337500</v>
       </c>
       <c r="AE158">
-        <v>0.6</v>
+        <v>0.24</v>
       </c>
       <c r="AF158">
         <v>0</v>
       </c>
       <c r="AG158">
-        <v>235500</v>
+        <v>81000</v>
       </c>
       <c r="AH158">
-        <v>235500</v>
+        <v>81000</v>
       </c>
       <c r="AI158">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ158">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AK158">
         <v>0</v>
@@ -11956,58 +11956,58 @@
         <v>25</v>
       </c>
       <c r="D159" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E159">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F159" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G159" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H159">
-        <v>10004</v>
+        <v>10007</v>
       </c>
       <c r="I159" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J159">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K159" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L159" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB159">
-        <v>395000</v>
+        <v>337500</v>
       </c>
       <c r="AC159" s="1">
         <v>0</v>
       </c>
       <c r="AD159">
-        <v>395000</v>
+        <v>337500</v>
       </c>
       <c r="AE159">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="AF159">
         <v>0</v>
       </c>
       <c r="AG159">
-        <v>173800</v>
+        <v>243000</v>
       </c>
       <c r="AH159">
-        <v>173800</v>
+        <v>243000</v>
       </c>
       <c r="AI159">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ159">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK159">
         <v>0</v>
@@ -12024,31 +12024,31 @@
         <v>25</v>
       </c>
       <c r="D160" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E160">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F160" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G160" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H160">
-        <v>10004</v>
+        <v>10010</v>
       </c>
       <c r="I160" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J160">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K160" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L160" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB160">
         <v>402500</v>
@@ -12060,22 +12060,22 @@
         <v>402500</v>
       </c>
       <c r="AE160">
-        <v>1.56</v>
+        <v>0.12</v>
       </c>
       <c r="AF160">
         <v>0</v>
       </c>
       <c r="AG160">
-        <v>627900</v>
+        <v>48300</v>
       </c>
       <c r="AH160">
-        <v>627900</v>
+        <v>48300</v>
       </c>
       <c r="AI160">
         <v>2</v>
       </c>
       <c r="AJ160">
-        <v>0.78</v>
+        <v>0.06</v>
       </c>
       <c r="AK160">
         <v>0</v>
@@ -12092,58 +12092,58 @@
         <v>25</v>
       </c>
       <c r="D161" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E161">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F161" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G161" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H161">
-        <v>10005</v>
+        <v>11005</v>
       </c>
       <c r="I161" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J161">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K161" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L161" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB161">
-        <v>327500</v>
+        <v>205000</v>
       </c>
       <c r="AC161" s="1">
         <v>0</v>
       </c>
       <c r="AD161">
-        <v>327500</v>
+        <v>205000</v>
       </c>
       <c r="AE161">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="AF161">
         <v>0</v>
       </c>
       <c r="AG161">
-        <v>196500</v>
+        <v>131200</v>
       </c>
       <c r="AH161">
-        <v>196500</v>
+        <v>131200</v>
       </c>
       <c r="AI161">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ161">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="AK161">
         <v>0</v>
@@ -12169,31 +12169,31 @@
         <v>87</v>
       </c>
       <c r="G162" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H162">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I162" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J162">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K162" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L162" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB162">
-        <v>330000</v>
+        <v>327500</v>
       </c>
       <c r="AC162" s="1">
         <v>0</v>
       </c>
       <c r="AD162">
-        <v>330000</v>
+        <v>327500</v>
       </c>
       <c r="AE162">
         <v>0.4</v>
@@ -12202,16 +12202,16 @@
         <v>0</v>
       </c>
       <c r="AG162">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="AH162">
-        <v>132000</v>
+        <v>131000</v>
       </c>
       <c r="AI162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ162">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AK162">
         <v>0</v>
@@ -12237,49 +12237,49 @@
         <v>87</v>
       </c>
       <c r="G163" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H163">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I163" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J163">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K163" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L163" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB163">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC163" s="1">
         <v>0</v>
       </c>
       <c r="AD163">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE163">
-        <v>2.04</v>
+        <v>0.48</v>
       </c>
       <c r="AF163">
         <v>0</v>
       </c>
       <c r="AG163">
-        <v>688500</v>
+        <v>158400</v>
       </c>
       <c r="AH163">
-        <v>688500</v>
+        <v>158400</v>
       </c>
       <c r="AI163">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ163">
-        <v>0.14000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AK163">
         <v>0</v>
@@ -12305,49 +12305,49 @@
         <v>87</v>
       </c>
       <c r="G164" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="H164">
-        <v>10007</v>
+        <v>10001</v>
       </c>
       <c r="I164" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J164">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K164" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L164" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB164">
-        <v>327500</v>
+        <v>337500</v>
       </c>
       <c r="AC164" s="1">
         <v>0</v>
       </c>
       <c r="AD164">
-        <v>327500</v>
+        <v>337500</v>
       </c>
       <c r="AE164">
-        <v>0.4</v>
+        <v>1.36</v>
       </c>
       <c r="AF164">
         <v>0</v>
       </c>
       <c r="AG164">
-        <v>131000</v>
+        <v>459000</v>
       </c>
       <c r="AH164">
-        <v>131000</v>
+        <v>459000</v>
       </c>
       <c r="AI164">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AJ164">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="AK164">
         <v>0</v>
@@ -12373,43 +12373,43 @@
         <v>87</v>
       </c>
       <c r="G165" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H165">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="I165" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J165">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K165" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L165" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB165">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AC165" s="1">
         <v>0</v>
       </c>
       <c r="AD165">
-        <v>330000</v>
+        <v>337500</v>
       </c>
       <c r="AE165">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AF165">
         <v>0</v>
       </c>
       <c r="AG165">
-        <v>26400</v>
+        <v>13500</v>
       </c>
       <c r="AH165">
-        <v>26400</v>
+        <v>13500</v>
       </c>
       <c r="AI165">
         <v>0</v>
@@ -12441,49 +12441,49 @@
         <v>87</v>
       </c>
       <c r="G166" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="H166">
-        <v>10007</v>
+        <v>10004</v>
       </c>
       <c r="I166" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J166">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K166" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L166" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB166">
-        <v>337500</v>
+        <v>392500</v>
       </c>
       <c r="AC166" s="1">
         <v>0</v>
       </c>
       <c r="AD166">
-        <v>337500</v>
+        <v>392500</v>
       </c>
       <c r="AE166">
-        <v>0.32</v>
+        <v>0.6</v>
       </c>
       <c r="AF166">
         <v>0</v>
       </c>
       <c r="AG166">
-        <v>108000</v>
+        <v>235500</v>
       </c>
       <c r="AH166">
-        <v>108000</v>
+        <v>235500</v>
       </c>
       <c r="AI166">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ166">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AK166">
         <v>0</v>
@@ -12509,43 +12509,43 @@
         <v>87</v>
       </c>
       <c r="G167" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="H167">
-        <v>10008</v>
+        <v>10004</v>
       </c>
       <c r="I167" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="J167">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K167" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L167" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB167">
-        <v>237500</v>
+        <v>395000</v>
       </c>
       <c r="AC167" s="1">
         <v>0</v>
       </c>
       <c r="AD167">
-        <v>237500</v>
+        <v>395000</v>
       </c>
       <c r="AE167">
-        <v>0.04</v>
+        <v>0.44</v>
       </c>
       <c r="AF167">
         <v>0</v>
       </c>
       <c r="AG167">
-        <v>9500</v>
+        <v>173800</v>
       </c>
       <c r="AH167">
-        <v>9500</v>
+        <v>173800</v>
       </c>
       <c r="AI167">
         <v>0</v>
@@ -12577,22 +12577,22 @@
         <v>87</v>
       </c>
       <c r="G168" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H168">
-        <v>10010</v>
+        <v>10004</v>
       </c>
       <c r="I168" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J168">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K168" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L168" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB168">
         <v>402500</v>
@@ -12604,22 +12604,22 @@
         <v>402500</v>
       </c>
       <c r="AE168">
-        <v>0.04</v>
+        <v>1.64</v>
       </c>
       <c r="AF168">
         <v>0</v>
       </c>
       <c r="AG168">
-        <v>16100</v>
+        <v>660100</v>
       </c>
       <c r="AH168">
-        <v>16100</v>
+        <v>660100</v>
       </c>
       <c r="AI168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ168">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AK168">
         <v>0</v>
@@ -12645,49 +12645,49 @@
         <v>87</v>
       </c>
       <c r="G169" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="H169">
-        <v>11005</v>
+        <v>10005</v>
       </c>
       <c r="I169" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="J169">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="K169" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L169" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="AB169">
-        <v>205000</v>
+        <v>327500</v>
       </c>
       <c r="AC169" s="1">
         <v>0</v>
       </c>
       <c r="AD169">
-        <v>205000</v>
+        <v>327500</v>
       </c>
       <c r="AE169">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
       <c r="AF169">
         <v>0</v>
       </c>
       <c r="AG169">
-        <v>73800</v>
+        <v>196500</v>
       </c>
       <c r="AH169">
-        <v>73800</v>
+        <v>196500</v>
       </c>
       <c r="AI169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ169">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="AK169">
         <v>0</v>
@@ -12704,58 +12704,58 @@
         <v>25</v>
       </c>
       <c r="D170" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E170">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F170" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G170" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H170">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I170" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J170">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K170" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L170" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB170">
-        <v>327500</v>
+        <v>330000</v>
       </c>
       <c r="AC170" s="1">
         <v>0</v>
       </c>
       <c r="AD170">
-        <v>327500</v>
+        <v>330000</v>
       </c>
       <c r="AE170">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AF170">
         <v>0</v>
       </c>
       <c r="AG170">
-        <v>196500</v>
+        <v>132000</v>
       </c>
       <c r="AH170">
-        <v>196500</v>
+        <v>132000</v>
       </c>
       <c r="AI170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ170">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK170">
         <v>0</v>
@@ -12772,31 +12772,31 @@
         <v>25</v>
       </c>
       <c r="D171" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E171">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F171" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G171" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H171">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I171" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J171">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K171" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L171" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB171">
         <v>337500</v>
@@ -12808,22 +12808,22 @@
         <v>337500</v>
       </c>
       <c r="AE171">
-        <v>1.5640000000000001</v>
+        <v>2.44</v>
       </c>
       <c r="AF171">
         <v>0</v>
       </c>
       <c r="AG171">
-        <v>527850</v>
+        <v>823500</v>
       </c>
       <c r="AH171">
-        <v>527850</v>
+        <v>823500</v>
       </c>
       <c r="AI171">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AJ171">
-        <v>0.26</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK171">
         <v>0</v>
@@ -12840,31 +12840,31 @@
         <v>25</v>
       </c>
       <c r="D172" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E172">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F172" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G172" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H172">
-        <v>10002</v>
+        <v>10007</v>
       </c>
       <c r="I172" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J172">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K172" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L172" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB172">
         <v>327500</v>
@@ -12876,22 +12876,22 @@
         <v>327500</v>
       </c>
       <c r="AE172">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AF172">
         <v>0</v>
       </c>
       <c r="AG172">
-        <v>65500</v>
+        <v>131000</v>
       </c>
       <c r="AH172">
-        <v>65500</v>
+        <v>131000</v>
       </c>
       <c r="AI172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ172">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AK172">
         <v>0</v>
@@ -12908,58 +12908,58 @@
         <v>25</v>
       </c>
       <c r="D173" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E173">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F173" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G173" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="H173">
-        <v>10002</v>
+        <v>10007</v>
       </c>
       <c r="I173" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="J173">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K173" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L173" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB173">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AC173" s="1">
         <v>0</v>
       </c>
       <c r="AD173">
-        <v>337500</v>
+        <v>330000</v>
       </c>
       <c r="AE173">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="AF173">
         <v>0</v>
       </c>
       <c r="AG173">
-        <v>74250</v>
+        <v>26400</v>
       </c>
       <c r="AH173">
-        <v>74250</v>
+        <v>26400</v>
       </c>
       <c r="AI173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ173">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AK173">
         <v>0</v>
@@ -12976,58 +12976,58 @@
         <v>25</v>
       </c>
       <c r="D174" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E174">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G174" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H174">
-        <v>10003</v>
+        <v>10007</v>
       </c>
       <c r="I174" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="J174">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K174" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L174" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB174">
-        <v>327500</v>
+        <v>337500</v>
       </c>
       <c r="AC174" s="1">
         <v>0</v>
       </c>
       <c r="AD174">
-        <v>327500</v>
+        <v>337500</v>
       </c>
       <c r="AE174">
-        <v>0.12</v>
+        <v>0.44</v>
       </c>
       <c r="AF174">
         <v>0</v>
       </c>
       <c r="AG174">
-        <v>39300</v>
+        <v>148500</v>
       </c>
       <c r="AH174">
-        <v>39300</v>
+        <v>148500</v>
       </c>
       <c r="AI174">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ174">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="AK174">
         <v>0</v>
@@ -13044,58 +13044,58 @@
         <v>25</v>
       </c>
       <c r="D175" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E175">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F175" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G175" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="H175">
-        <v>10003</v>
+        <v>10008</v>
       </c>
       <c r="I175" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="J175">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K175" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L175" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB175">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AC175" s="1">
         <v>0</v>
       </c>
       <c r="AD175">
-        <v>337500</v>
+        <v>237500</v>
       </c>
       <c r="AE175">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AF175">
         <v>0</v>
       </c>
       <c r="AG175">
-        <v>27000</v>
+        <v>9500</v>
       </c>
       <c r="AH175">
-        <v>27000</v>
+        <v>9500</v>
       </c>
       <c r="AI175">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ175">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="AK175">
         <v>0</v>
@@ -13112,40 +13112,40 @@
         <v>25</v>
       </c>
       <c r="D176" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E176">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F176" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G176" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="H176">
-        <v>10004</v>
+        <v>10010</v>
       </c>
       <c r="I176" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J176">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K176" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L176" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB176">
-        <v>392500</v>
+        <v>402500</v>
       </c>
       <c r="AC176" s="1">
         <v>0</v>
       </c>
       <c r="AD176">
-        <v>392500</v>
+        <v>402500</v>
       </c>
       <c r="AE176">
         <v>0.08</v>
@@ -13154,16 +13154,16 @@
         <v>0</v>
       </c>
       <c r="AG176">
-        <v>31400</v>
+        <v>32200</v>
       </c>
       <c r="AH176">
-        <v>31400</v>
+        <v>32200</v>
       </c>
       <c r="AI176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ176">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AK176">
         <v>0</v>
@@ -13180,58 +13180,58 @@
         <v>25</v>
       </c>
       <c r="D177" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E177">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F177" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G177" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="H177">
-        <v>10004</v>
+        <v>11005</v>
       </c>
       <c r="I177" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="J177">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K177" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L177" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB177">
-        <v>402500</v>
+        <v>205000</v>
       </c>
       <c r="AC177" s="1">
         <v>0</v>
       </c>
       <c r="AD177">
-        <v>402500</v>
+        <v>205000</v>
       </c>
       <c r="AE177">
-        <v>1.26</v>
+        <v>0.36</v>
       </c>
       <c r="AF177">
         <v>0</v>
       </c>
       <c r="AG177">
-        <v>507150</v>
+        <v>73800</v>
       </c>
       <c r="AH177">
-        <v>507150</v>
+        <v>73800</v>
       </c>
       <c r="AI177">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AJ177">
-        <v>0.11</v>
+        <v>0.36</v>
       </c>
       <c r="AK177">
         <v>0</v>
@@ -13257,22 +13257,22 @@
         <v>89</v>
       </c>
       <c r="G178" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H178">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I178" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J178">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K178" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L178" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB178">
         <v>327500</v>
@@ -13284,22 +13284,22 @@
         <v>327500</v>
       </c>
       <c r="AE178">
-        <v>1.68</v>
+        <v>0.6</v>
       </c>
       <c r="AF178">
         <v>0</v>
       </c>
       <c r="AG178">
-        <v>550200</v>
+        <v>196500</v>
       </c>
       <c r="AH178">
-        <v>550200</v>
+        <v>196500</v>
       </c>
       <c r="AI178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ178">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AK178">
         <v>0</v>
@@ -13325,22 +13325,22 @@
         <v>89</v>
       </c>
       <c r="G179" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="H179">
-        <v>10005</v>
+        <v>10001</v>
       </c>
       <c r="I179" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="J179">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K179" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L179" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB179">
         <v>337500</v>
@@ -13352,22 +13352,22 @@
         <v>337500</v>
       </c>
       <c r="AE179">
-        <v>1.98</v>
+        <v>1.5640000000000001</v>
       </c>
       <c r="AF179">
         <v>0</v>
       </c>
       <c r="AG179">
-        <v>668250</v>
+        <v>527850</v>
       </c>
       <c r="AH179">
-        <v>668250</v>
+        <v>527850</v>
       </c>
       <c r="AI179">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AJ179">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="AK179">
         <v>0</v>
@@ -13393,22 +13393,22 @@
         <v>89</v>
       </c>
       <c r="G180" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H180">
-        <v>10006</v>
+        <v>10002</v>
       </c>
       <c r="I180" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J180">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K180" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L180" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB180">
         <v>327500</v>
@@ -13420,16 +13420,16 @@
         <v>327500</v>
       </c>
       <c r="AE180">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AF180">
         <v>0</v>
       </c>
       <c r="AG180">
-        <v>13100</v>
+        <v>65500</v>
       </c>
       <c r="AH180">
-        <v>13100</v>
+        <v>65500</v>
       </c>
       <c r="AI180">
         <v>0</v>
@@ -13461,22 +13461,22 @@
         <v>89</v>
       </c>
       <c r="G181" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="H181">
-        <v>10006</v>
+        <v>10002</v>
       </c>
       <c r="I181" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="J181">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K181" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L181" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB181">
         <v>337500</v>
@@ -13488,22 +13488,22 @@
         <v>337500</v>
       </c>
       <c r="AE181">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AF181">
         <v>0</v>
       </c>
       <c r="AG181">
-        <v>67500</v>
+        <v>74250</v>
       </c>
       <c r="AH181">
-        <v>67500</v>
+        <v>74250</v>
       </c>
       <c r="AI181">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ181">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK181">
         <v>0</v>
@@ -13529,49 +13529,49 @@
         <v>89</v>
       </c>
       <c r="G182" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H182">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="I182" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J182">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K182" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L182" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB182">
-        <v>337500</v>
+        <v>327500</v>
       </c>
       <c r="AC182" s="1">
         <v>0</v>
       </c>
       <c r="AD182">
-        <v>337500</v>
+        <v>327500</v>
       </c>
       <c r="AE182">
-        <v>0.48</v>
+        <v>0.12</v>
       </c>
       <c r="AF182">
         <v>0</v>
       </c>
       <c r="AG182">
-        <v>162000</v>
+        <v>39300</v>
       </c>
       <c r="AH182">
-        <v>162000</v>
+        <v>39300</v>
       </c>
       <c r="AI182">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AJ182">
-        <v>7.0000000000000007E-2</v>
+        <v>0.12</v>
       </c>
       <c r="AK182">
         <v>0</v>
@@ -13597,46 +13597,46 @@
         <v>89</v>
       </c>
       <c r="G183" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H183">
-        <v>10008</v>
+        <v>10003</v>
       </c>
       <c r="I183" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="J183">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K183" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L183" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB183">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AC183" s="1">
         <v>0</v>
       </c>
       <c r="AD183">
-        <v>237500</v>
+        <v>337500</v>
       </c>
       <c r="AE183">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="AF183">
         <v>0</v>
       </c>
       <c r="AG183">
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="AH183">
-        <v>28500</v>
+        <v>27000</v>
       </c>
       <c r="AI183">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ183">
         <v>0.04</v>
@@ -13665,49 +13665,49 @@
         <v>89</v>
       </c>
       <c r="G184" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="H184">
-        <v>10010</v>
+        <v>10004</v>
       </c>
       <c r="I184" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J184">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K184" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L184" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB184">
-        <v>402500</v>
+        <v>392500</v>
       </c>
       <c r="AC184" s="1">
         <v>0</v>
       </c>
       <c r="AD184">
-        <v>402500</v>
+        <v>392500</v>
       </c>
       <c r="AE184">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="AF184">
         <v>0</v>
       </c>
       <c r="AG184">
-        <v>136850</v>
+        <v>31400</v>
       </c>
       <c r="AH184">
-        <v>136850</v>
+        <v>31400</v>
       </c>
       <c r="AI184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ184">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AK184">
         <v>0</v>
@@ -13733,49 +13733,49 @@
         <v>89</v>
       </c>
       <c r="G185" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H185">
-        <v>11005</v>
+        <v>10004</v>
       </c>
       <c r="I185" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J185">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K185" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L185" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB185">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AC185" s="1">
         <v>0</v>
       </c>
       <c r="AD185">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AE185">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AF185">
         <v>0</v>
       </c>
       <c r="AG185">
-        <v>270600</v>
+        <v>507150</v>
       </c>
       <c r="AH185">
-        <v>270600</v>
+        <v>507150</v>
       </c>
       <c r="AI185">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ185">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AK185">
         <v>0</v>
@@ -13792,58 +13792,58 @@
         <v>25</v>
       </c>
       <c r="D186" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E186">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F186" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G186" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H186">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I186" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J186">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K186" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L186" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB186">
-        <v>333750</v>
+        <v>327500</v>
       </c>
       <c r="AC186" s="1">
         <v>0</v>
       </c>
       <c r="AD186">
-        <v>333750</v>
+        <v>327500</v>
       </c>
       <c r="AE186">
-        <v>0.12</v>
+        <v>1.68</v>
       </c>
       <c r="AF186">
         <v>0</v>
       </c>
       <c r="AG186">
-        <v>40050</v>
+        <v>550200</v>
       </c>
       <c r="AH186">
-        <v>40050</v>
+        <v>550200</v>
       </c>
       <c r="AI186">
         <v>1</v>
       </c>
       <c r="AJ186">
-        <v>0.12</v>
+        <v>1.68</v>
       </c>
       <c r="AK186">
         <v>0</v>
@@ -13860,31 +13860,31 @@
         <v>25</v>
       </c>
       <c r="D187" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E187">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F187" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G187" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H187">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I187" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J187">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K187" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L187" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB187">
         <v>337500</v>
@@ -13896,22 +13896,22 @@
         <v>337500</v>
       </c>
       <c r="AE187">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AF187">
         <v>0</v>
       </c>
       <c r="AG187">
-        <v>459000</v>
+        <v>681750</v>
       </c>
       <c r="AH187">
-        <v>459000</v>
+        <v>681750</v>
       </c>
       <c r="AI187">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ187">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AK187">
         <v>0</v>
@@ -13928,52 +13928,52 @@
         <v>25</v>
       </c>
       <c r="D188" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E188">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F188" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G188" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="H188">
-        <v>10002</v>
+        <v>10006</v>
       </c>
       <c r="I188" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="J188">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K188" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L188" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB188">
-        <v>337500</v>
+        <v>327500</v>
       </c>
       <c r="AC188" s="1">
         <v>0</v>
       </c>
       <c r="AD188">
-        <v>337500</v>
+        <v>327500</v>
       </c>
       <c r="AE188">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="AF188">
         <v>0</v>
       </c>
       <c r="AG188">
-        <v>27000</v>
+        <v>13100</v>
       </c>
       <c r="AH188">
-        <v>27000</v>
+        <v>13100</v>
       </c>
       <c r="AI188">
         <v>0</v>
@@ -13996,52 +13996,52 @@
         <v>25</v>
       </c>
       <c r="D189" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E189">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F189" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G189" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="H189">
-        <v>10003</v>
+        <v>10006</v>
       </c>
       <c r="I189" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="J189">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K189" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L189" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB189">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AC189" s="1">
         <v>0</v>
       </c>
       <c r="AD189">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AE189">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AF189">
         <v>0</v>
       </c>
       <c r="AG189">
-        <v>13350</v>
+        <v>67500</v>
       </c>
       <c r="AH189">
-        <v>13350</v>
+        <v>67500</v>
       </c>
       <c r="AI189">
         <v>0</v>
@@ -14064,31 +14064,31 @@
         <v>25</v>
       </c>
       <c r="D190" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E190">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F190" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G190" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="H190">
-        <v>10003</v>
+        <v>10007</v>
       </c>
       <c r="I190" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="J190">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K190" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L190" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB190">
         <v>337500</v>
@@ -14100,22 +14100,22 @@
         <v>337500</v>
       </c>
       <c r="AE190">
-        <v>0.28000000000000003</v>
+        <v>0.48</v>
       </c>
       <c r="AF190">
         <v>0</v>
       </c>
       <c r="AG190">
-        <v>94500</v>
+        <v>162000</v>
       </c>
       <c r="AH190">
-        <v>94500</v>
+        <v>162000</v>
       </c>
       <c r="AI190">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AJ190">
-        <v>0.14000000000000001</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK190">
         <v>0</v>
@@ -14132,58 +14132,58 @@
         <v>25</v>
       </c>
       <c r="D191" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E191">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F191" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G191" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H191">
-        <v>10004</v>
+        <v>10008</v>
       </c>
       <c r="I191" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="J191">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K191" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L191" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB191">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AC191" s="1">
         <v>0</v>
       </c>
       <c r="AD191">
-        <v>402500</v>
+        <v>237500</v>
       </c>
       <c r="AE191">
-        <v>0.6</v>
+        <v>0.12</v>
       </c>
       <c r="AF191">
         <v>0</v>
       </c>
       <c r="AG191">
-        <v>241500</v>
+        <v>28500</v>
       </c>
       <c r="AH191">
-        <v>241500</v>
+        <v>28500</v>
       </c>
       <c r="AI191">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AJ191">
-        <v>7.0000000000000007E-2</v>
+        <v>0.04</v>
       </c>
       <c r="AK191">
         <v>0</v>
@@ -14200,22 +14200,22 @@
         <v>25</v>
       </c>
       <c r="D192" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E192">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F192" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G192" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="H192">
-        <v>10005</v>
+        <v>10010</v>
       </c>
       <c r="I192" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J192">
         <v>1003</v>
@@ -14227,25 +14227,25 @@
         <v>35</v>
       </c>
       <c r="AB192">
-        <v>333750</v>
+        <v>402500</v>
       </c>
       <c r="AC192" s="1">
         <v>0</v>
       </c>
       <c r="AD192">
-        <v>333750</v>
+        <v>402500</v>
       </c>
       <c r="AE192">
-        <v>0.16</v>
+        <v>0.34</v>
       </c>
       <c r="AF192">
         <v>0</v>
       </c>
       <c r="AG192">
-        <v>53400</v>
+        <v>136850</v>
       </c>
       <c r="AH192">
-        <v>53400</v>
+        <v>136850</v>
       </c>
       <c r="AI192">
         <v>0</v>
@@ -14268,58 +14268,58 @@
         <v>25</v>
       </c>
       <c r="D193" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E193">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F193" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="G193" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H193">
-        <v>10005</v>
+        <v>11005</v>
       </c>
       <c r="I193" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="J193">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="K193" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="L193" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="AB193">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AC193" s="1">
         <v>0</v>
       </c>
       <c r="AD193">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AE193">
-        <v>1.76</v>
+        <v>1.32</v>
       </c>
       <c r="AF193">
         <v>0</v>
       </c>
       <c r="AG193">
-        <v>594000</v>
+        <v>270600</v>
       </c>
       <c r="AH193">
-        <v>594000</v>
+        <v>270600</v>
       </c>
       <c r="AI193">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AJ193">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AK193">
         <v>0</v>
@@ -14345,22 +14345,22 @@
         <v>91</v>
       </c>
       <c r="G194" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H194">
-        <v>10006</v>
+        <v>10001</v>
       </c>
       <c r="I194" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J194">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K194" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L194" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB194">
         <v>333750</v>
@@ -14372,22 +14372,22 @@
         <v>333750</v>
       </c>
       <c r="AE194">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="AF194">
         <v>0</v>
       </c>
       <c r="AG194">
-        <v>13350</v>
+        <v>40050</v>
       </c>
       <c r="AH194">
-        <v>13350</v>
+        <v>40050</v>
       </c>
       <c r="AI194">
         <v>1</v>
       </c>
       <c r="AJ194">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="AK194">
         <v>0</v>
@@ -14413,22 +14413,22 @@
         <v>91</v>
       </c>
       <c r="G195" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="H195">
-        <v>10006</v>
+        <v>10001</v>
       </c>
       <c r="I195" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="J195">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="K195" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="L195" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AB195">
         <v>337500</v>
@@ -14440,22 +14440,22 @@
         <v>337500</v>
       </c>
       <c r="AE195">
-        <v>0.2</v>
+        <v>1.36</v>
       </c>
       <c r="AF195">
         <v>0</v>
       </c>
       <c r="AG195">
-        <v>67500</v>
+        <v>459000</v>
       </c>
       <c r="AH195">
-        <v>67500</v>
+        <v>459000</v>
       </c>
       <c r="AI195">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="AJ195">
-        <v>7.0000000000000007E-2</v>
+        <v>0.1</v>
       </c>
       <c r="AK195">
         <v>0</v>
@@ -14481,43 +14481,43 @@
         <v>91</v>
       </c>
       <c r="G196" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="H196">
-        <v>10007</v>
+        <v>10002</v>
       </c>
       <c r="I196" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="J196">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K196" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L196" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB196">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AC196" s="1">
         <v>0</v>
       </c>
       <c r="AD196">
-        <v>333750</v>
+        <v>337500</v>
       </c>
       <c r="AE196">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="AF196">
         <v>0</v>
       </c>
       <c r="AG196">
-        <v>13350</v>
+        <v>27000</v>
       </c>
       <c r="AH196">
-        <v>13350</v>
+        <v>27000</v>
       </c>
       <c r="AI196">
         <v>0</v>
@@ -14549,49 +14549,49 @@
         <v>91</v>
       </c>
       <c r="G197" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="H197">
-        <v>10007</v>
+        <v>10003</v>
       </c>
       <c r="I197" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="J197">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K197" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L197" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB197">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC197" s="1">
         <v>0</v>
       </c>
       <c r="AD197">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE197">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="AF197">
         <v>0</v>
       </c>
       <c r="AG197">
-        <v>67500</v>
+        <v>13350</v>
       </c>
       <c r="AH197">
-        <v>67500</v>
+        <v>13350</v>
       </c>
       <c r="AI197">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ197">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="AK197">
         <v>0</v>
@@ -14617,22 +14617,22 @@
         <v>91</v>
       </c>
       <c r="G198" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="H198">
-        <v>10009</v>
+        <v>10003</v>
       </c>
       <c r="I198" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="J198">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="K198" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="L198" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="AB198">
         <v>337500</v>
@@ -14644,22 +14644,22 @@
         <v>337500</v>
       </c>
       <c r="AE198">
-        <v>0.04</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="AF198">
         <v>0</v>
       </c>
       <c r="AG198">
-        <v>13500</v>
+        <v>94500</v>
       </c>
       <c r="AH198">
-        <v>13500</v>
+        <v>94500</v>
       </c>
       <c r="AI198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ198">
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK198">
         <v>0</v>
@@ -14685,31 +14685,31 @@
         <v>91</v>
       </c>
       <c r="G199" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="H199">
-        <v>11005</v>
+        <v>10004</v>
       </c>
       <c r="I199" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="J199">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="K199" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="L199" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="AB199">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AC199" s="1">
         <v>0</v>
       </c>
       <c r="AD199">
-        <v>205000</v>
+        <v>402500</v>
       </c>
       <c r="AE199">
         <v>0.68</v>
@@ -14718,10 +14718,10 @@
         <v>0</v>
       </c>
       <c r="AG199">
-        <v>139400</v>
+        <v>273700</v>
       </c>
       <c r="AH199">
-        <v>139400</v>
+        <v>273700</v>
       </c>
       <c r="AI199">
         <v>10</v>
@@ -14744,58 +14744,58 @@
         <v>25</v>
       </c>
       <c r="D200" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E200">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F200" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G200" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="H200">
-        <v>10001</v>
+        <v>10005</v>
       </c>
       <c r="I200" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="J200">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K200" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L200" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB200">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC200" s="1">
         <v>0</v>
       </c>
       <c r="AD200">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE200">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="AF200">
         <v>0</v>
       </c>
       <c r="AG200">
-        <v>121500</v>
+        <v>53400</v>
       </c>
       <c r="AH200">
-        <v>121500</v>
+        <v>53400</v>
       </c>
       <c r="AI200">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ200">
-        <v>7.0000000000000007E-2</v>
+        <v>0</v>
       </c>
       <c r="AK200">
         <v>0</v>
@@ -14812,55 +14812,55 @@
         <v>25</v>
       </c>
       <c r="D201" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E201">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F201" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G201" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="H201">
-        <v>10004</v>
+        <v>10005</v>
       </c>
       <c r="I201" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J201">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="K201" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="L201" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="AB201">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AC201" s="1">
         <v>0</v>
       </c>
       <c r="AD201">
-        <v>402500</v>
+        <v>337500</v>
       </c>
       <c r="AE201">
-        <v>0.32</v>
+        <v>1.76</v>
       </c>
       <c r="AF201">
         <v>0</v>
       </c>
       <c r="AG201">
-        <v>128800</v>
+        <v>594000</v>
       </c>
       <c r="AH201">
-        <v>128800</v>
+        <v>594000</v>
       </c>
       <c r="AI201">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AJ201">
         <v>0.08</v>
@@ -14880,22 +14880,22 @@
         <v>25</v>
       </c>
       <c r="D202" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E202">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F202" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G202" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H202">
-        <v>10005</v>
+        <v>10006</v>
       </c>
       <c r="I202" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="J202">
         <v>1003</v>
@@ -14907,31 +14907,31 @@
         <v>35</v>
       </c>
       <c r="AB202">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC202" s="1">
         <v>0</v>
       </c>
       <c r="AD202">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE202">
-        <v>1.84</v>
+        <v>0.04</v>
       </c>
       <c r="AF202">
         <v>0</v>
       </c>
       <c r="AG202">
-        <v>621000</v>
+        <v>13350</v>
       </c>
       <c r="AH202">
-        <v>621000</v>
+        <v>13350</v>
       </c>
       <c r="AI202">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AJ202">
-        <v>0.14000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="AK202">
         <v>0</v>
@@ -14948,13 +14948,13 @@
         <v>25</v>
       </c>
       <c r="D203" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E203">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F203" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G203" t="s">
         <v>36</v>
@@ -14984,22 +14984,22 @@
         <v>337500</v>
       </c>
       <c r="AE203">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AF203">
         <v>0</v>
       </c>
       <c r="AG203">
-        <v>13500</v>
+        <v>67500</v>
       </c>
       <c r="AH203">
-        <v>13500</v>
+        <v>67500</v>
       </c>
       <c r="AI203">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AJ203">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK203">
         <v>0</v>
@@ -15016,13 +15016,13 @@
         <v>25</v>
       </c>
       <c r="D204" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E204">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F204" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G204" t="s">
         <v>38</v>
@@ -15043,31 +15043,31 @@
         <v>41</v>
       </c>
       <c r="AB204">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AC204" s="1">
         <v>0</v>
       </c>
       <c r="AD204">
-        <v>337500</v>
+        <v>333750</v>
       </c>
       <c r="AE204">
-        <v>0.24</v>
+        <v>0.04</v>
       </c>
       <c r="AF204">
         <v>0</v>
       </c>
       <c r="AG204">
-        <v>81000</v>
+        <v>13350</v>
       </c>
       <c r="AH204">
-        <v>81000</v>
+        <v>13350</v>
       </c>
       <c r="AI204">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AJ204">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="AK204">
         <v>0</v>
@@ -15084,58 +15084,58 @@
         <v>25</v>
       </c>
       <c r="D205" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E205">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F205" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G205" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H205">
-        <v>11005</v>
+        <v>10007</v>
       </c>
       <c r="I205" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="J205">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="K205" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L205" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AB205">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AC205" s="1">
         <v>0</v>
       </c>
       <c r="AD205">
-        <v>205000</v>
+        <v>337500</v>
       </c>
       <c r="AE205">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
       <c r="AF205">
         <v>0</v>
       </c>
       <c r="AG205">
-        <v>246000</v>
+        <v>67500</v>
       </c>
       <c r="AH205">
-        <v>246000</v>
+        <v>67500</v>
       </c>
       <c r="AI205">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AJ205">
-        <v>0.15</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK205">
         <v>0</v>
@@ -15152,31 +15152,31 @@
         <v>25</v>
       </c>
       <c r="D206" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E206">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F206" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G206" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H206">
-        <v>10001</v>
+        <v>10009</v>
       </c>
       <c r="I206" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="J206">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="K206" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L206" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="AB206">
         <v>337500</v>
@@ -15188,22 +15188,22 @@
         <v>337500</v>
       </c>
       <c r="AE206">
-        <v>1.72</v>
+        <v>0.04</v>
       </c>
       <c r="AF206">
         <v>0</v>
       </c>
       <c r="AG206">
-        <v>580500</v>
+        <v>13500</v>
       </c>
       <c r="AH206">
-        <v>580500</v>
+        <v>13500</v>
       </c>
       <c r="AI206">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AJ206">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AK206">
         <v>0</v>
@@ -15220,58 +15220,58 @@
         <v>25</v>
       </c>
       <c r="D207" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E207">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F207" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G207" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="H207">
-        <v>10002</v>
+        <v>11005</v>
       </c>
       <c r="I207" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="J207">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="K207" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="L207" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="AB207">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AC207" s="1">
         <v>0</v>
       </c>
       <c r="AD207">
-        <v>337500</v>
+        <v>205000</v>
       </c>
       <c r="AE207">
-        <v>0.08</v>
+        <v>0.68</v>
       </c>
       <c r="AF207">
         <v>0</v>
       </c>
       <c r="AG207">
-        <v>27000</v>
+        <v>139400</v>
       </c>
       <c r="AH207">
-        <v>27000</v>
+        <v>139400</v>
       </c>
       <c r="AI207">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="AJ207">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK207">
         <v>0</v>
@@ -15288,22 +15288,22 @@
         <v>25</v>
       </c>
       <c r="D208" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E208">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F208" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G208" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H208">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="I208" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J208">
         <v>1005</v>
@@ -15324,22 +15324,22 @@
         <v>337500</v>
       </c>
       <c r="AE208">
-        <v>0.04</v>
+        <v>0.36</v>
       </c>
       <c r="AF208">
         <v>0</v>
       </c>
       <c r="AG208">
-        <v>13500</v>
+        <v>121500</v>
       </c>
       <c r="AH208">
-        <v>13500</v>
+        <v>121500</v>
       </c>
       <c r="AI208">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AJ208">
-        <v>0.04</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="AK208">
         <v>0</v>
@@ -15356,13 +15356,13 @@
         <v>25</v>
       </c>
       <c r="D209" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E209">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F209" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G209" t="s">
         <v>28</v>
@@ -15392,22 +15392,22 @@
         <v>402500</v>
       </c>
       <c r="AE209">
-        <v>0.72</v>
+        <v>0.32</v>
       </c>
       <c r="AF209">
         <v>0</v>
       </c>
       <c r="AG209">
-        <v>289800</v>
+        <v>128800</v>
       </c>
       <c r="AH209">
-        <v>289800</v>
+        <v>128800</v>
       </c>
       <c r="AI209">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AJ209">
-        <v>7.0000000000000007E-2</v>
+        <v>0.08</v>
       </c>
       <c r="AK209">
         <v>0</v>
@@ -15424,13 +15424,13 @@
         <v>25</v>
       </c>
       <c r="D210" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E210">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F210" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G210" t="s">
         <v>32</v>
@@ -15460,22 +15460,22 @@
         <v>337500</v>
       </c>
       <c r="AE210">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AF210">
         <v>0</v>
       </c>
       <c r="AG210">
-        <v>594000</v>
+        <v>621000</v>
       </c>
       <c r="AH210">
-        <v>594000</v>
+        <v>621000</v>
       </c>
       <c r="AI210">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AJ210">
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="AK210">
         <v>0</v>
@@ -15492,13 +15492,13 @@
         <v>25</v>
       </c>
       <c r="D211" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E211">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F211" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G211" t="s">
         <v>36</v>
@@ -15560,13 +15560,13 @@
         <v>25</v>
       </c>
       <c r="D212" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E212">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F212" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G212" t="s">
         <v>38</v>
@@ -15596,22 +15596,22 @@
         <v>337500</v>
       </c>
       <c r="AE212">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="AF212">
         <v>0</v>
       </c>
       <c r="AG212">
-        <v>27000</v>
+        <v>81000</v>
       </c>
       <c r="AH212">
-        <v>27000</v>
+        <v>81000</v>
       </c>
       <c r="AI212">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AJ212">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="AK212">
         <v>0</v>
@@ -15628,13 +15628,13 @@
         <v>25</v>
       </c>
       <c r="D213" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E213">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F213" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G213" t="s">
         <v>48</v>
@@ -15664,24 +15664,636 @@
         <v>205000</v>
       </c>
       <c r="AE213">
-        <v>0.52</v>
+        <v>1.2</v>
       </c>
       <c r="AF213">
         <v>0</v>
       </c>
       <c r="AG213">
-        <v>106600</v>
+        <v>246000</v>
       </c>
       <c r="AH213">
-        <v>106600</v>
+        <v>246000</v>
       </c>
       <c r="AI213">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AJ213">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="AK213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>24</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>25</v>
+      </c>
+      <c r="D214" t="s">
+        <v>94</v>
+      </c>
+      <c r="E214">
+        <v>21</v>
+      </c>
+      <c r="F214" t="s">
+        <v>95</v>
+      </c>
+      <c r="G214" t="s">
+        <v>52</v>
+      </c>
+      <c r="H214">
+        <v>10001</v>
+      </c>
+      <c r="I214" t="s">
+        <v>53</v>
+      </c>
+      <c r="J214">
+        <v>1005</v>
+      </c>
+      <c r="K214" t="s">
+        <v>30</v>
+      </c>
+      <c r="L214" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB214">
+        <v>337500</v>
+      </c>
+      <c r="AC214" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD214">
+        <v>337500</v>
+      </c>
+      <c r="AE214">
+        <v>2.12</v>
+      </c>
+      <c r="AF214">
+        <v>0</v>
+      </c>
+      <c r="AG214">
+        <v>715500</v>
+      </c>
+      <c r="AH214">
+        <v>715500</v>
+      </c>
+      <c r="AI214">
+        <v>20</v>
+      </c>
+      <c r="AJ214">
+        <v>0.11</v>
+      </c>
+      <c r="AK214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>24</v>
+      </c>
+      <c r="B215">
+        <v>1</v>
+      </c>
+      <c r="C215" t="s">
+        <v>25</v>
+      </c>
+      <c r="D215" t="s">
+        <v>94</v>
+      </c>
+      <c r="E215">
+        <v>21</v>
+      </c>
+      <c r="F215" t="s">
+        <v>95</v>
+      </c>
+      <c r="G215" t="s">
+        <v>54</v>
+      </c>
+      <c r="H215">
+        <v>10002</v>
+      </c>
+      <c r="I215" t="s">
+        <v>55</v>
+      </c>
+      <c r="J215">
+        <v>1005</v>
+      </c>
+      <c r="K215" t="s">
+        <v>30</v>
+      </c>
+      <c r="L215" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB215">
+        <v>337500</v>
+      </c>
+      <c r="AC215" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD215">
+        <v>337500</v>
+      </c>
+      <c r="AE215">
+        <v>0.12</v>
+      </c>
+      <c r="AF215">
+        <v>0</v>
+      </c>
+      <c r="AG215">
+        <v>40500</v>
+      </c>
+      <c r="AH215">
+        <v>40500</v>
+      </c>
+      <c r="AI215">
+        <v>3</v>
+      </c>
+      <c r="AJ215">
+        <v>0.04</v>
+      </c>
+      <c r="AK215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>24</v>
+      </c>
+      <c r="B216">
+        <v>1</v>
+      </c>
+      <c r="C216" t="s">
+        <v>25</v>
+      </c>
+      <c r="D216" t="s">
+        <v>94</v>
+      </c>
+      <c r="E216">
+        <v>21</v>
+      </c>
+      <c r="F216" t="s">
+        <v>95</v>
+      </c>
+      <c r="G216" t="s">
+        <v>56</v>
+      </c>
+      <c r="H216">
+        <v>10003</v>
+      </c>
+      <c r="I216" t="s">
+        <v>57</v>
+      </c>
+      <c r="J216">
+        <v>1005</v>
+      </c>
+      <c r="K216" t="s">
+        <v>30</v>
+      </c>
+      <c r="L216" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB216">
+        <v>337500</v>
+      </c>
+      <c r="AC216" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD216">
+        <v>337500</v>
+      </c>
+      <c r="AE216">
+        <v>0.04</v>
+      </c>
+      <c r="AF216">
+        <v>0</v>
+      </c>
+      <c r="AG216">
+        <v>13500</v>
+      </c>
+      <c r="AH216">
+        <v>13500</v>
+      </c>
+      <c r="AI216">
+        <v>1</v>
+      </c>
+      <c r="AJ216">
+        <v>0.04</v>
+      </c>
+      <c r="AK216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>24</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217" t="s">
+        <v>25</v>
+      </c>
+      <c r="D217" t="s">
+        <v>94</v>
+      </c>
+      <c r="E217">
+        <v>21</v>
+      </c>
+      <c r="F217" t="s">
+        <v>95</v>
+      </c>
+      <c r="G217" t="s">
+        <v>28</v>
+      </c>
+      <c r="H217">
+        <v>10004</v>
+      </c>
+      <c r="I217" t="s">
+        <v>29</v>
+      </c>
+      <c r="J217">
+        <v>1005</v>
+      </c>
+      <c r="K217" t="s">
+        <v>30</v>
+      </c>
+      <c r="L217" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB217">
+        <v>402500</v>
+      </c>
+      <c r="AC217" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD217">
+        <v>402500</v>
+      </c>
+      <c r="AE217">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="AF217">
+        <v>0</v>
+      </c>
+      <c r="AG217">
+        <v>466900</v>
+      </c>
+      <c r="AH217">
+        <v>466900</v>
+      </c>
+      <c r="AI217">
+        <v>16</v>
+      </c>
+      <c r="AJ217">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="AK217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>24</v>
+      </c>
+      <c r="B218">
+        <v>1</v>
+      </c>
+      <c r="C218" t="s">
+        <v>25</v>
+      </c>
+      <c r="D218" t="s">
+        <v>94</v>
+      </c>
+      <c r="E218">
+        <v>21</v>
+      </c>
+      <c r="F218" t="s">
+        <v>95</v>
+      </c>
+      <c r="G218" t="s">
+        <v>32</v>
+      </c>
+      <c r="H218">
+        <v>10005</v>
+      </c>
+      <c r="I218" t="s">
+        <v>33</v>
+      </c>
+      <c r="J218">
+        <v>1003</v>
+      </c>
+      <c r="K218" t="s">
+        <v>34</v>
+      </c>
+      <c r="L218" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB218">
+        <v>337500</v>
+      </c>
+      <c r="AC218" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD218">
+        <v>337500</v>
+      </c>
+      <c r="AE218">
+        <v>1.84</v>
+      </c>
+      <c r="AF218">
+        <v>0</v>
+      </c>
+      <c r="AG218">
+        <v>621000</v>
+      </c>
+      <c r="AH218">
+        <v>621000</v>
+      </c>
+      <c r="AI218">
+        <v>12</v>
+      </c>
+      <c r="AJ218">
+        <v>0.15</v>
+      </c>
+      <c r="AK218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>24</v>
+      </c>
+      <c r="B219">
+        <v>1</v>
+      </c>
+      <c r="C219" t="s">
+        <v>25</v>
+      </c>
+      <c r="D219" t="s">
+        <v>94</v>
+      </c>
+      <c r="E219">
+        <v>21</v>
+      </c>
+      <c r="F219" t="s">
+        <v>95</v>
+      </c>
+      <c r="G219" t="s">
+        <v>36</v>
+      </c>
+      <c r="H219">
+        <v>10006</v>
+      </c>
+      <c r="I219" t="s">
+        <v>37</v>
+      </c>
+      <c r="J219">
+        <v>1003</v>
+      </c>
+      <c r="K219" t="s">
+        <v>34</v>
+      </c>
+      <c r="L219" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB219">
+        <v>337500</v>
+      </c>
+      <c r="AC219" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD219">
+        <v>337500</v>
+      </c>
+      <c r="AE219">
+        <v>0.04</v>
+      </c>
+      <c r="AF219">
+        <v>0</v>
+      </c>
+      <c r="AG219">
+        <v>13500</v>
+      </c>
+      <c r="AH219">
+        <v>13500</v>
+      </c>
+      <c r="AI219">
+        <v>1</v>
+      </c>
+      <c r="AJ219">
+        <v>0.04</v>
+      </c>
+      <c r="AK219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>24</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220" t="s">
+        <v>25</v>
+      </c>
+      <c r="D220" t="s">
+        <v>94</v>
+      </c>
+      <c r="E220">
+        <v>21</v>
+      </c>
+      <c r="F220" t="s">
+        <v>95</v>
+      </c>
+      <c r="G220" t="s">
+        <v>38</v>
+      </c>
+      <c r="H220">
+        <v>10007</v>
+      </c>
+      <c r="I220" t="s">
+        <v>39</v>
+      </c>
+      <c r="J220">
+        <v>1004</v>
+      </c>
+      <c r="K220" t="s">
+        <v>40</v>
+      </c>
+      <c r="L220" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB220">
+        <v>337500</v>
+      </c>
+      <c r="AC220" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD220">
+        <v>337500</v>
+      </c>
+      <c r="AE220">
+        <v>0.08</v>
+      </c>
+      <c r="AF220">
+        <v>0</v>
+      </c>
+      <c r="AG220">
+        <v>27000</v>
+      </c>
+      <c r="AH220">
+        <v>27000</v>
+      </c>
+      <c r="AI220">
+        <v>2</v>
+      </c>
+      <c r="AJ220">
+        <v>0.04</v>
+      </c>
+      <c r="AK220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221">
+        <v>1</v>
+      </c>
+      <c r="C221" t="s">
+        <v>25</v>
+      </c>
+      <c r="D221" t="s">
+        <v>94</v>
+      </c>
+      <c r="E221">
+        <v>21</v>
+      </c>
+      <c r="F221" t="s">
+        <v>95</v>
+      </c>
+      <c r="G221" t="s">
+        <v>60</v>
+      </c>
+      <c r="H221">
+        <v>10009</v>
+      </c>
+      <c r="I221" t="s">
+        <v>61</v>
+      </c>
+      <c r="J221">
+        <v>1004</v>
+      </c>
+      <c r="K221" t="s">
+        <v>40</v>
+      </c>
+      <c r="L221" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB221">
+        <v>337500</v>
+      </c>
+      <c r="AC221" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD221">
+        <v>337500</v>
+      </c>
+      <c r="AE221">
+        <v>0.04</v>
+      </c>
+      <c r="AF221">
+        <v>0</v>
+      </c>
+      <c r="AG221">
+        <v>13500</v>
+      </c>
+      <c r="AH221">
+        <v>13500</v>
+      </c>
+      <c r="AI221">
+        <v>1</v>
+      </c>
+      <c r="AJ221">
+        <v>0.04</v>
+      </c>
+      <c r="AK221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>24</v>
+      </c>
+      <c r="B222">
+        <v>1</v>
+      </c>
+      <c r="C222" t="s">
+        <v>25</v>
+      </c>
+      <c r="D222" t="s">
+        <v>94</v>
+      </c>
+      <c r="E222">
+        <v>21</v>
+      </c>
+      <c r="F222" t="s">
+        <v>95</v>
+      </c>
+      <c r="G222" t="s">
+        <v>48</v>
+      </c>
+      <c r="H222">
+        <v>11005</v>
+      </c>
+      <c r="I222" t="s">
+        <v>49</v>
+      </c>
+      <c r="J222">
+        <v>1006</v>
+      </c>
+      <c r="K222" t="s">
+        <v>44</v>
+      </c>
+      <c r="L222" t="s">
+        <v>45</v>
+      </c>
+      <c r="AB222">
+        <v>205000</v>
+      </c>
+      <c r="AC222" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD222">
+        <v>205000</v>
+      </c>
+      <c r="AE222">
+        <v>0.88</v>
+      </c>
+      <c r="AF222">
+        <v>0</v>
+      </c>
+      <c r="AG222">
+        <v>180400</v>
+      </c>
+      <c r="AH222">
+        <v>180400</v>
+      </c>
+      <c r="AI222">
+        <v>8</v>
+      </c>
+      <c r="AJ222">
+        <v>0.11</v>
+      </c>
+      <c r="AK222">
         <v>0</v>
       </c>
     </row>
